--- a/wwwroot/ExcelModel/Ovs_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Ovs_PHY_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95046D61-DF56-4396-8EC9-9AFA4F1B72B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE7ED4B-6168-4FA7-9EFA-40336F634882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="444">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -1973,10 +1973,6 @@
     <t>Time(s)</t>
   </si>
   <si>
-    <t>After 10 washing</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t># 1</t>
   </si>
   <si>
@@ -3105,6 +3101,9 @@
   <si>
     <t>ISO 9237</t>
     <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>washing</t>
   </si>
 </sst>
 </file>
@@ -4554,6 +4553,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4561,9 +4563,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4626,22 +4625,22 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5763,7 +5762,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="67" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
@@ -5802,7 +5801,7 @@
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1">
       <c r="A3" s="22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I3" s="143"/>
       <c r="J3" s="143"/>
@@ -5835,13 +5834,13 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" s="22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B4" s="61"/>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
       <c r="E4" s="57" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F4" s="61"/>
       <c r="G4" s="61"/>
@@ -5879,7 +5878,7 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B5" s="61"/>
       <c r="C5" s="61"/>
@@ -6176,10 +6175,10 @@
     </row>
     <row r="12" spans="1:38">
       <c r="A12" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="49" t="s">
         <v>297</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>298</v>
       </c>
       <c r="D12" s="29"/>
       <c r="E12" s="29"/>
@@ -6219,12 +6218,12 @@
     </row>
     <row r="13" spans="1:38">
       <c r="A13" s="77" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:38">
       <c r="A14" s="77" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -6234,12 +6233,12 @@
     </row>
     <row r="17" spans="1:38">
       <c r="A17" s="67" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:38">
       <c r="A18" s="22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I18" s="143"/>
       <c r="J18" s="143"/>
@@ -6261,13 +6260,13 @@
     </row>
     <row r="19" spans="1:38">
       <c r="A19" s="22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
       <c r="D19" s="61"/>
       <c r="E19" s="57" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F19" s="61"/>
       <c r="G19" s="61"/>
@@ -6277,12 +6276,12 @@
     </row>
     <row r="20" spans="1:38">
       <c r="A20" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:38">
       <c r="A21" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:38">
@@ -6293,7 +6292,7 @@
       <c r="C22" s="172"/>
       <c r="D22" s="173"/>
       <c r="E22" s="177" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F22" s="172"/>
       <c r="G22" s="172"/>
@@ -6325,7 +6324,7 @@
       <c r="AG22" s="172"/>
       <c r="AH22" s="173"/>
       <c r="AI22" s="146" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AJ22" s="172"/>
       <c r="AK22" s="172"/>
@@ -6693,22 +6692,22 @@
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="22" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="49" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -6865,7 +6864,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="67" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
@@ -6912,23 +6911,23 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" s="22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1"/>
     <row r="6" spans="1:38" ht="15" customHeight="1">
       <c r="A6" s="89" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="89" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="21.15" customHeight="1">
       <c r="A8" s="46" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B8" s="90"/>
       <c r="C8" s="90"/>
@@ -6970,7 +6969,7 @@
     </row>
     <row r="9" spans="1:38" ht="21.15" customHeight="1">
       <c r="A9" s="234" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B9" s="234"/>
       <c r="C9" s="234"/>
@@ -7028,31 +7027,31 @@
       <c r="K10" s="234"/>
       <c r="L10" s="234"/>
       <c r="M10" s="234" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N10" s="234"/>
       <c r="O10" s="234"/>
       <c r="P10" s="234"/>
       <c r="Q10" s="234" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="R10" s="234"/>
       <c r="S10" s="234"/>
       <c r="T10" s="234"/>
       <c r="U10" s="234" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V10" s="234"/>
       <c r="W10" s="234"/>
       <c r="X10" s="234"/>
       <c r="Y10" s="234" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z10" s="234"/>
       <c r="AA10" s="234"/>
       <c r="AB10" s="234"/>
       <c r="AC10" s="234" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD10" s="234"/>
       <c r="AE10" s="234"/>
@@ -7071,7 +7070,7 @@
       <c r="D11" s="165"/>
       <c r="E11" s="166"/>
       <c r="F11" s="154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G11" s="155"/>
       <c r="H11" s="155"/>
@@ -7113,7 +7112,7 @@
       <c r="D12" s="143"/>
       <c r="E12" s="171"/>
       <c r="F12" s="154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G12" s="155"/>
       <c r="H12" s="155"/>
@@ -7155,7 +7154,7 @@
       <c r="D13" s="165"/>
       <c r="E13" s="166"/>
       <c r="F13" s="154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G13" s="155"/>
       <c r="H13" s="155"/>
@@ -7197,7 +7196,7 @@
       <c r="D14" s="143"/>
       <c r="E14" s="171"/>
       <c r="F14" s="154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G14" s="155"/>
       <c r="H14" s="155"/>
@@ -7239,7 +7238,7 @@
       <c r="D15" s="165"/>
       <c r="E15" s="166"/>
       <c r="F15" s="154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G15" s="155"/>
       <c r="H15" s="155"/>
@@ -7281,7 +7280,7 @@
       <c r="D16" s="143"/>
       <c r="E16" s="171"/>
       <c r="F16" s="154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G16" s="155"/>
       <c r="H16" s="155"/>
@@ -7318,7 +7317,7 @@
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1">
       <c r="A17" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B17" s="46"/>
       <c r="C17" s="46"/>
@@ -8846,7 +8845,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="82" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B2" s="83"/>
       <c r="C2" s="83"/>
@@ -8928,7 +8927,7 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" s="84" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B4" s="84"/>
       <c r="C4" s="84"/>
@@ -8970,7 +8969,7 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="84" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B5" s="84"/>
       <c r="C5" s="84"/>
@@ -9012,7 +9011,7 @@
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
       <c r="A6" s="84" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B6" s="84"/>
       <c r="C6" s="84"/>
@@ -9054,7 +9053,7 @@
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="84" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B7" s="84"/>
       <c r="C7" s="84"/>
@@ -9136,7 +9135,7 @@
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1">
       <c r="A9" s="84" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B9" s="84"/>
       <c r="C9" s="84"/>
@@ -9178,7 +9177,7 @@
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1">
       <c r="A10" s="84" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B10" s="84"/>
       <c r="C10" s="84"/>
@@ -9220,7 +9219,7 @@
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1">
       <c r="A11" s="84" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B11" s="84"/>
       <c r="C11" s="84"/>
@@ -9262,7 +9261,7 @@
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1">
       <c r="A12" s="179" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B12" s="179"/>
       <c r="C12" s="179"/>
@@ -9318,35 +9317,35 @@
       <c r="I13" s="179"/>
       <c r="J13" s="179"/>
       <c r="K13" s="183" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L13" s="183"/>
       <c r="M13" s="183"/>
       <c r="N13" s="183"/>
       <c r="O13" s="183"/>
       <c r="P13" s="183" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q13" s="183"/>
       <c r="R13" s="183"/>
       <c r="S13" s="183"/>
       <c r="T13" s="183"/>
       <c r="U13" s="183" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V13" s="183"/>
       <c r="W13" s="183"/>
       <c r="X13" s="183"/>
       <c r="Y13" s="183"/>
       <c r="Z13" s="183" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AA13" s="183"/>
       <c r="AB13" s="183"/>
       <c r="AC13" s="183"/>
       <c r="AD13" s="183"/>
       <c r="AE13" s="183" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AF13" s="183"/>
       <c r="AG13" s="183"/>
@@ -9360,7 +9359,7 @@
       <c r="A14" s="164"/>
       <c r="B14" s="166"/>
       <c r="C14" s="235" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D14" s="235"/>
       <c r="E14" s="235"/>
@@ -9402,7 +9401,7 @@
       <c r="A15" s="170"/>
       <c r="B15" s="171"/>
       <c r="C15" s="235" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D15" s="235"/>
       <c r="E15" s="235"/>
@@ -9444,7 +9443,7 @@
       <c r="A16" s="164"/>
       <c r="B16" s="166"/>
       <c r="C16" s="235" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D16" s="235"/>
       <c r="E16" s="235"/>
@@ -9486,7 +9485,7 @@
       <c r="A17" s="170"/>
       <c r="B17" s="171"/>
       <c r="C17" s="235" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D17" s="235"/>
       <c r="E17" s="235"/>
@@ -9528,7 +9527,7 @@
       <c r="A18" s="164"/>
       <c r="B18" s="166"/>
       <c r="C18" s="235" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D18" s="235"/>
       <c r="E18" s="235"/>
@@ -9570,7 +9569,7 @@
       <c r="A19" s="170"/>
       <c r="B19" s="171"/>
       <c r="C19" s="235" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D19" s="235"/>
       <c r="E19" s="235"/>
@@ -9610,7 +9609,7 @@
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1">
       <c r="A20" s="84" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B20" s="84"/>
       <c r="C20" s="84"/>
@@ -9652,7 +9651,7 @@
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1">
       <c r="A21" s="84" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B21" s="84"/>
       <c r="C21" s="84"/>
@@ -9736,7 +9735,7 @@
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1">
       <c r="A23" s="87" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B23" s="84"/>
       <c r="C23" s="84"/>
@@ -9778,7 +9777,7 @@
       <c r="B24" s="84"/>
       <c r="C24" s="84"/>
       <c r="D24" s="88" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E24" s="84"/>
       <c r="F24" s="84"/>
@@ -15304,7 +15303,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4303F6F2-CAB3-437A-AAF1-DB1CEC16E34E}">
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="7" width="2.33203125" style="22" customWidth="1"/>
@@ -15556,7 +15555,7 @@
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
       <c r="A7" s="24" t="s">
-        <v>286</v>
+        <v>59</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -15651,35 +15650,35 @@
       <c r="G9" s="207"/>
       <c r="H9" s="208"/>
       <c r="I9" s="245" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J9" s="183"/>
       <c r="K9" s="183"/>
       <c r="L9" s="183"/>
       <c r="M9" s="183"/>
       <c r="N9" s="245" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O9" s="183"/>
       <c r="P9" s="183"/>
       <c r="Q9" s="183"/>
       <c r="R9" s="183"/>
       <c r="S9" s="245" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T9" s="183"/>
       <c r="U9" s="183"/>
       <c r="V9" s="183"/>
       <c r="W9" s="183"/>
       <c r="X9" s="245" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y9" s="183"/>
       <c r="Z9" s="183"/>
       <c r="AA9" s="183"/>
       <c r="AB9" s="183"/>
       <c r="AC9" s="245" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD9" s="183"/>
       <c r="AE9" s="183"/>
@@ -15977,147 +15976,535 @@
       <c r="AM16" s="37"/>
     </row>
     <row r="17" spans="1:40">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" s="175"/>
+      <c r="E17" s="175"/>
+      <c r="F17" s="56" t="s">
+        <v>443</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="25"/>
+      <c r="AK17" s="25"/>
+      <c r="AL17" s="25"/>
+      <c r="AM17" s="37"/>
+    </row>
+    <row r="18" spans="1:40">
+      <c r="A18" s="200" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="201"/>
+      <c r="C18" s="201"/>
+      <c r="D18" s="201"/>
+      <c r="E18" s="201"/>
+      <c r="F18" s="201"/>
+      <c r="G18" s="201"/>
+      <c r="H18" s="202"/>
+      <c r="I18" s="245" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="183"/>
+      <c r="K18" s="183"/>
+      <c r="L18" s="183"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="183"/>
+      <c r="O18" s="183"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="183"/>
+      <c r="R18" s="183"/>
+      <c r="S18" s="183"/>
+      <c r="T18" s="183"/>
+      <c r="U18" s="183"/>
+      <c r="V18" s="183"/>
+      <c r="W18" s="183"/>
+      <c r="X18" s="183"/>
+      <c r="Y18" s="183"/>
+      <c r="Z18" s="183"/>
+      <c r="AA18" s="183"/>
+      <c r="AB18" s="183"/>
+      <c r="AC18" s="183"/>
+      <c r="AD18" s="183"/>
+      <c r="AE18" s="183"/>
+      <c r="AF18" s="183"/>
+      <c r="AG18" s="183"/>
+      <c r="AH18" s="141" t="s">
+        <v>215</v>
+      </c>
+      <c r="AI18" s="141"/>
+      <c r="AJ18" s="141"/>
+      <c r="AK18" s="141"/>
+      <c r="AL18" s="141"/>
+      <c r="AM18" s="141"/>
+    </row>
+    <row r="19" spans="1:40">
+      <c r="A19" s="206"/>
+      <c r="B19" s="207"/>
+      <c r="C19" s="207"/>
+      <c r="D19" s="207"/>
+      <c r="E19" s="207"/>
+      <c r="F19" s="207"/>
+      <c r="G19" s="207"/>
+      <c r="H19" s="208"/>
+      <c r="I19" s="245" t="s">
+        <v>286</v>
+      </c>
+      <c r="J19" s="183"/>
+      <c r="K19" s="183"/>
+      <c r="L19" s="183"/>
+      <c r="M19" s="183"/>
+      <c r="N19" s="245" t="s">
+        <v>287</v>
+      </c>
+      <c r="O19" s="183"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="183"/>
+      <c r="R19" s="183"/>
+      <c r="S19" s="245" t="s">
+        <v>288</v>
+      </c>
+      <c r="T19" s="183"/>
+      <c r="U19" s="183"/>
+      <c r="V19" s="183"/>
+      <c r="W19" s="183"/>
+      <c r="X19" s="245" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y19" s="183"/>
+      <c r="Z19" s="183"/>
+      <c r="AA19" s="183"/>
+      <c r="AB19" s="183"/>
+      <c r="AC19" s="245" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD19" s="183"/>
+      <c r="AE19" s="183"/>
+      <c r="AF19" s="183"/>
+      <c r="AG19" s="183"/>
+      <c r="AH19" s="141"/>
+      <c r="AI19" s="141"/>
+      <c r="AJ19" s="141"/>
+      <c r="AK19" s="141"/>
+      <c r="AL19" s="141"/>
+      <c r="AM19" s="141"/>
+    </row>
+    <row r="20" spans="1:40">
+      <c r="A20" s="144"/>
+      <c r="B20" s="144"/>
+      <c r="C20" s="144"/>
+      <c r="D20" s="144"/>
+      <c r="E20" s="144"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="144"/>
+      <c r="H20" s="144"/>
+      <c r="I20" s="183"/>
+      <c r="J20" s="183"/>
+      <c r="K20" s="183"/>
+      <c r="L20" s="183"/>
+      <c r="M20" s="183"/>
+      <c r="N20" s="183"/>
+      <c r="O20" s="183"/>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="183"/>
+      <c r="R20" s="183"/>
+      <c r="S20" s="183"/>
+      <c r="T20" s="183"/>
+      <c r="U20" s="183"/>
+      <c r="V20" s="183"/>
+      <c r="W20" s="183"/>
+      <c r="X20" s="183"/>
+      <c r="Y20" s="183"/>
+      <c r="Z20" s="183"/>
+      <c r="AA20" s="183"/>
+      <c r="AB20" s="183"/>
+      <c r="AC20" s="183"/>
+      <c r="AD20" s="183"/>
+      <c r="AE20" s="183"/>
+      <c r="AF20" s="183"/>
+      <c r="AG20" s="183"/>
+      <c r="AH20" s="184"/>
+      <c r="AI20" s="184"/>
+      <c r="AJ20" s="184"/>
+      <c r="AK20" s="184"/>
+      <c r="AL20" s="184"/>
+      <c r="AM20" s="184"/>
+    </row>
+    <row r="21" spans="1:40">
+      <c r="A21" s="144"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="183"/>
+      <c r="J21" s="183"/>
+      <c r="K21" s="183"/>
+      <c r="L21" s="183"/>
+      <c r="M21" s="183"/>
+      <c r="N21" s="183"/>
+      <c r="O21" s="183"/>
+      <c r="P21" s="183"/>
+      <c r="Q21" s="183"/>
+      <c r="R21" s="183"/>
+      <c r="S21" s="183"/>
+      <c r="T21" s="183"/>
+      <c r="U21" s="183"/>
+      <c r="V21" s="183"/>
+      <c r="W21" s="183"/>
+      <c r="X21" s="183"/>
+      <c r="Y21" s="183"/>
+      <c r="Z21" s="183"/>
+      <c r="AA21" s="183"/>
+      <c r="AB21" s="183"/>
+      <c r="AC21" s="183"/>
+      <c r="AD21" s="183"/>
+      <c r="AE21" s="183"/>
+      <c r="AF21" s="183"/>
+      <c r="AG21" s="183"/>
+      <c r="AH21" s="184"/>
+      <c r="AI21" s="184"/>
+      <c r="AJ21" s="184"/>
+      <c r="AK21" s="184"/>
+      <c r="AL21" s="184"/>
+      <c r="AM21" s="184"/>
+    </row>
+    <row r="22" spans="1:40">
+      <c r="A22" s="144"/>
+      <c r="B22" s="144"/>
+      <c r="C22" s="144"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="144"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="183"/>
+      <c r="J22" s="183"/>
+      <c r="K22" s="183"/>
+      <c r="L22" s="183"/>
+      <c r="M22" s="183"/>
+      <c r="N22" s="183"/>
+      <c r="O22" s="183"/>
+      <c r="P22" s="183"/>
+      <c r="Q22" s="183"/>
+      <c r="R22" s="183"/>
+      <c r="S22" s="183"/>
+      <c r="T22" s="183"/>
+      <c r="U22" s="183"/>
+      <c r="V22" s="183"/>
+      <c r="W22" s="183"/>
+      <c r="X22" s="183"/>
+      <c r="Y22" s="183"/>
+      <c r="Z22" s="183"/>
+      <c r="AA22" s="183"/>
+      <c r="AB22" s="183"/>
+      <c r="AC22" s="183"/>
+      <c r="AD22" s="183"/>
+      <c r="AE22" s="183"/>
+      <c r="AF22" s="183"/>
+      <c r="AG22" s="183"/>
+      <c r="AH22" s="184"/>
+      <c r="AI22" s="184"/>
+      <c r="AJ22" s="184"/>
+      <c r="AK22" s="184"/>
+      <c r="AL22" s="184"/>
+      <c r="AM22" s="184"/>
+      <c r="AN22" s="70"/>
+    </row>
+    <row r="23" spans="1:40">
+      <c r="A23" s="144"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="183"/>
+      <c r="J23" s="183"/>
+      <c r="K23" s="183"/>
+      <c r="L23" s="183"/>
+      <c r="M23" s="183"/>
+      <c r="N23" s="183"/>
+      <c r="O23" s="183"/>
+      <c r="P23" s="183"/>
+      <c r="Q23" s="183"/>
+      <c r="R23" s="183"/>
+      <c r="S23" s="183"/>
+      <c r="T23" s="183"/>
+      <c r="U23" s="183"/>
+      <c r="V23" s="183"/>
+      <c r="W23" s="183"/>
+      <c r="X23" s="183"/>
+      <c r="Y23" s="183"/>
+      <c r="Z23" s="183"/>
+      <c r="AA23" s="183"/>
+      <c r="AB23" s="183"/>
+      <c r="AC23" s="183"/>
+      <c r="AD23" s="183"/>
+      <c r="AE23" s="183"/>
+      <c r="AF23" s="183"/>
+      <c r="AG23" s="183"/>
+      <c r="AH23" s="184"/>
+      <c r="AI23" s="184"/>
+      <c r="AJ23" s="184"/>
+      <c r="AK23" s="184"/>
+      <c r="AL23" s="184"/>
+      <c r="AM23" s="184"/>
+    </row>
+    <row r="24" spans="1:40">
+      <c r="A24" s="144"/>
+      <c r="B24" s="144"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="183"/>
+      <c r="J24" s="183"/>
+      <c r="K24" s="183"/>
+      <c r="L24" s="183"/>
+      <c r="M24" s="183"/>
+      <c r="N24" s="183"/>
+      <c r="O24" s="183"/>
+      <c r="P24" s="183"/>
+      <c r="Q24" s="183"/>
+      <c r="R24" s="183"/>
+      <c r="S24" s="183"/>
+      <c r="T24" s="183"/>
+      <c r="U24" s="183"/>
+      <c r="V24" s="183"/>
+      <c r="W24" s="183"/>
+      <c r="X24" s="183"/>
+      <c r="Y24" s="183"/>
+      <c r="Z24" s="183"/>
+      <c r="AA24" s="183"/>
+      <c r="AB24" s="183"/>
+      <c r="AC24" s="183"/>
+      <c r="AD24" s="183"/>
+      <c r="AE24" s="183"/>
+      <c r="AF24" s="183"/>
+      <c r="AG24" s="183"/>
+      <c r="AH24" s="184"/>
+      <c r="AI24" s="184"/>
+      <c r="AJ24" s="184"/>
+      <c r="AK24" s="184"/>
+      <c r="AL24" s="184"/>
+      <c r="AM24" s="184"/>
+    </row>
+    <row r="25" spans="1:40">
+      <c r="A25" s="144"/>
+      <c r="B25" s="144"/>
+      <c r="C25" s="144"/>
+      <c r="D25" s="144"/>
+      <c r="E25" s="144"/>
+      <c r="F25" s="144"/>
+      <c r="G25" s="144"/>
+      <c r="H25" s="144"/>
+      <c r="I25" s="183"/>
+      <c r="J25" s="183"/>
+      <c r="K25" s="183"/>
+      <c r="L25" s="183"/>
+      <c r="M25" s="183"/>
+      <c r="N25" s="183"/>
+      <c r="O25" s="183"/>
+      <c r="P25" s="183"/>
+      <c r="Q25" s="183"/>
+      <c r="R25" s="183"/>
+      <c r="S25" s="183"/>
+      <c r="T25" s="183"/>
+      <c r="U25" s="183"/>
+      <c r="V25" s="183"/>
+      <c r="W25" s="183"/>
+      <c r="X25" s="183"/>
+      <c r="Y25" s="183"/>
+      <c r="Z25" s="183"/>
+      <c r="AA25" s="183"/>
+      <c r="AB25" s="183"/>
+      <c r="AC25" s="183"/>
+      <c r="AD25" s="183"/>
+      <c r="AE25" s="183"/>
+      <c r="AF25" s="183"/>
+      <c r="AG25" s="183"/>
+      <c r="AH25" s="184"/>
+      <c r="AI25" s="184"/>
+      <c r="AJ25" s="184"/>
+      <c r="AK25" s="184"/>
+      <c r="AL25" s="184"/>
+      <c r="AM25" s="184"/>
+    </row>
+    <row r="26" spans="1:40">
+      <c r="A26" s="48" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:40">
-      <c r="A18" s="48"/>
-    </row>
-    <row r="19" spans="1:40">
-      <c r="A19" s="108" t="s">
+    <row r="27" spans="1:40">
+      <c r="A27" s="48"/>
+    </row>
+    <row r="28" spans="1:40">
+      <c r="A28" s="108" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="29" spans="1:40">
+      <c r="A29" s="22" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="20" spans="1:40">
-      <c r="A20" s="22" t="s">
+      <c r="G29" s="143"/>
+      <c r="H29" s="143"/>
+      <c r="I29" s="109" t="s">
         <v>433</v>
       </c>
-      <c r="G20" s="143"/>
-      <c r="H20" s="143"/>
-      <c r="I20" s="109" t="s">
+      <c r="AJ29" s="143"/>
+      <c r="AK29" s="143"/>
+      <c r="AL29" s="143"/>
+    </row>
+    <row r="30" spans="1:40">
+      <c r="A30" s="22" t="s">
         <v>434</v>
       </c>
-      <c r="AJ20" s="143"/>
-      <c r="AK20" s="143"/>
-      <c r="AL20" s="143"/>
-    </row>
-    <row r="21" spans="1:40">
-      <c r="A21" s="22" t="s">
+      <c r="Q30" s="143"/>
+      <c r="R30" s="143"/>
+      <c r="S30" s="143"/>
+      <c r="T30" s="143"/>
+      <c r="U30" s="143"/>
+      <c r="V30" s="143"/>
+      <c r="W30" s="143"/>
+      <c r="X30" s="143"/>
+      <c r="Y30" s="143"/>
+      <c r="Z30" s="143"/>
+      <c r="AA30" s="143"/>
+      <c r="AB30" s="143"/>
+      <c r="AC30" s="143"/>
+      <c r="AD30" s="110" t="s">
         <v>435</v>
       </c>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="143"/>
-      <c r="S21" s="143"/>
-      <c r="T21" s="143"/>
-      <c r="U21" s="143"/>
-      <c r="V21" s="143"/>
-      <c r="W21" s="143"/>
-      <c r="X21" s="143"/>
-      <c r="Y21" s="143"/>
-      <c r="Z21" s="143"/>
-      <c r="AA21" s="143"/>
-      <c r="AB21" s="143"/>
-      <c r="AC21" s="143"/>
-      <c r="AD21" s="110" t="s">
+    </row>
+    <row r="31" spans="1:40">
+      <c r="A31" s="109" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="22" spans="1:40">
-      <c r="A22" s="109" t="s">
+      <c r="B31" s="109"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="109"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="109"/>
+      <c r="J31" s="109"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="143"/>
+      <c r="N31" s="143"/>
+      <c r="O31" s="143"/>
+      <c r="P31" s="143"/>
+      <c r="Q31" s="232"/>
+      <c r="R31" s="232"/>
+      <c r="S31" s="232"/>
+      <c r="T31" s="22" t="s">
         <v>437</v>
       </c>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="143"/>
-      <c r="M22" s="143"/>
-      <c r="N22" s="143"/>
-      <c r="O22" s="143"/>
-      <c r="P22" s="143"/>
-      <c r="Q22" s="232"/>
-      <c r="R22" s="232"/>
-      <c r="S22" s="232"/>
-      <c r="T22" s="22" t="s">
+      <c r="U31" s="143"/>
+      <c r="V31" s="143"/>
+      <c r="W31" s="143"/>
+      <c r="X31" s="143"/>
+      <c r="Y31" s="143"/>
+      <c r="Z31" s="143"/>
+      <c r="AA31" s="22" t="s">
         <v>438</v>
       </c>
-      <c r="U22" s="143"/>
-      <c r="V22" s="143"/>
-      <c r="W22" s="143"/>
-      <c r="X22" s="143"/>
-      <c r="Y22" s="143"/>
-      <c r="Z22" s="143"/>
-      <c r="AA22" s="22" t="s">
-        <v>439</v>
-      </c>
-      <c r="AB22" s="111"/>
-      <c r="AC22" s="111"/>
-      <c r="AD22" s="111"/>
-      <c r="AE22" s="111"/>
-      <c r="AF22" s="111"/>
-      <c r="AG22" s="111"/>
-      <c r="AI22" s="112"/>
-      <c r="AJ22" s="112"/>
-      <c r="AK22" s="113"/>
-      <c r="AL22"/>
-      <c r="AM22" s="71"/>
-      <c r="AN22" s="70"/>
-    </row>
-    <row r="23" spans="1:40">
-      <c r="A23" s="249"/>
-      <c r="B23" s="249"/>
-      <c r="C23" s="249"/>
-      <c r="D23" s="249"/>
-      <c r="E23" s="249"/>
-      <c r="F23" s="249"/>
-      <c r="G23" s="249"/>
-      <c r="H23" s="249"/>
-      <c r="I23" s="249"/>
-      <c r="J23" s="249"/>
-      <c r="K23" s="249"/>
-      <c r="L23" s="249"/>
-      <c r="M23" s="249"/>
-      <c r="N23" s="249"/>
-      <c r="O23" s="249"/>
-      <c r="P23" s="249"/>
-      <c r="Q23" s="249"/>
-      <c r="R23" s="249"/>
-      <c r="S23" s="249"/>
-      <c r="T23" s="249"/>
-      <c r="U23" s="249"/>
-      <c r="V23" s="249"/>
-      <c r="W23" s="249"/>
-      <c r="X23" s="249"/>
-      <c r="Y23" s="249"/>
-      <c r="Z23" s="249"/>
-      <c r="AA23" s="249"/>
-      <c r="AB23" s="249"/>
-      <c r="AC23" s="249"/>
-      <c r="AD23" s="249"/>
-      <c r="AE23" s="249"/>
-      <c r="AF23" s="249"/>
-      <c r="AG23" s="249"/>
-      <c r="AH23" s="249"/>
-      <c r="AI23" s="249"/>
-      <c r="AJ23" s="249"/>
-      <c r="AK23" s="249"/>
-      <c r="AL23" s="249"/>
+      <c r="AB31" s="111"/>
+      <c r="AC31" s="111"/>
+      <c r="AD31" s="111"/>
+      <c r="AE31" s="111"/>
+      <c r="AF31" s="111"/>
+      <c r="AG31" s="111"/>
+      <c r="AI31" s="112"/>
+      <c r="AJ31" s="112"/>
+      <c r="AK31" s="113"/>
+      <c r="AL31"/>
+      <c r="AM31" s="71"/>
+    </row>
+    <row r="32" spans="1:40">
+      <c r="A32" s="246"/>
+      <c r="B32" s="246"/>
+      <c r="C32" s="246"/>
+      <c r="D32" s="246"/>
+      <c r="E32" s="246"/>
+      <c r="F32" s="246"/>
+      <c r="G32" s="246"/>
+      <c r="H32" s="246"/>
+      <c r="I32" s="246"/>
+      <c r="J32" s="246"/>
+      <c r="K32" s="246"/>
+      <c r="L32" s="246"/>
+      <c r="M32" s="246"/>
+      <c r="N32" s="246"/>
+      <c r="O32" s="246"/>
+      <c r="P32" s="246"/>
+      <c r="Q32" s="246"/>
+      <c r="R32" s="246"/>
+      <c r="S32" s="246"/>
+      <c r="T32" s="246"/>
+      <c r="U32" s="246"/>
+      <c r="V32" s="246"/>
+      <c r="W32" s="246"/>
+      <c r="X32" s="246"/>
+      <c r="Y32" s="246"/>
+      <c r="Z32" s="246"/>
+      <c r="AA32" s="246"/>
+      <c r="AB32" s="246"/>
+      <c r="AC32" s="246"/>
+      <c r="AD32" s="246"/>
+      <c r="AE32" s="246"/>
+      <c r="AF32" s="246"/>
+      <c r="AG32" s="246"/>
+      <c r="AH32" s="246"/>
+      <c r="AI32" s="246"/>
+      <c r="AJ32" s="246"/>
+      <c r="AK32" s="246"/>
+      <c r="AL32" s="246"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="A23:AL23"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="AJ20:AL20"/>
-    <mergeCell ref="Q21:AC21"/>
-    <mergeCell ref="L22:S22"/>
-    <mergeCell ref="U22:Z22"/>
+  <mergeCells count="109">
+    <mergeCell ref="A32:AL32"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="AJ29:AL29"/>
+    <mergeCell ref="Q30:AC30"/>
+    <mergeCell ref="L31:S31"/>
+    <mergeCell ref="U31:Z31"/>
+    <mergeCell ref="D17:E17"/>
     <mergeCell ref="AH14:AM14"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="I15:M15"/>
@@ -16132,7 +16519,6 @@
     <mergeCell ref="S14:W14"/>
     <mergeCell ref="X14:AB14"/>
     <mergeCell ref="AC14:AG14"/>
-    <mergeCell ref="AH12:AM12"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="I13:M13"/>
     <mergeCell ref="N13:R13"/>
@@ -16146,12 +16532,6 @@
     <mergeCell ref="S12:W12"/>
     <mergeCell ref="X12:AB12"/>
     <mergeCell ref="AC12:AG12"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="N11:R11"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="X11:AB11"/>
     <mergeCell ref="AC11:AG11"/>
     <mergeCell ref="AH11:AM11"/>
     <mergeCell ref="A10:H10"/>
@@ -16160,6 +16540,15 @@
     <mergeCell ref="S10:W10"/>
     <mergeCell ref="X10:AB10"/>
     <mergeCell ref="AC10:AG10"/>
+    <mergeCell ref="AH12:AM12"/>
+    <mergeCell ref="A18:H19"/>
+    <mergeCell ref="I18:AG18"/>
+    <mergeCell ref="AH18:AM19"/>
+    <mergeCell ref="I19:M19"/>
+    <mergeCell ref="N19:R19"/>
+    <mergeCell ref="S19:W19"/>
+    <mergeCell ref="X19:AB19"/>
+    <mergeCell ref="AC19:AG19"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A3:T3"/>
     <mergeCell ref="A8:H9"/>
@@ -16170,6 +16559,54 @@
     <mergeCell ref="S9:W9"/>
     <mergeCell ref="X9:AB9"/>
     <mergeCell ref="AC9:AG9"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="N11:R11"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="X11:AB11"/>
+    <mergeCell ref="AC20:AG20"/>
+    <mergeCell ref="AH20:AM20"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="I21:M21"/>
+    <mergeCell ref="N21:R21"/>
+    <mergeCell ref="S21:W21"/>
+    <mergeCell ref="X21:AB21"/>
+    <mergeCell ref="AC21:AG21"/>
+    <mergeCell ref="AH21:AM21"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="I20:M20"/>
+    <mergeCell ref="N20:R20"/>
+    <mergeCell ref="S20:W20"/>
+    <mergeCell ref="X20:AB20"/>
+    <mergeCell ref="AC22:AG22"/>
+    <mergeCell ref="AH22:AM22"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="I23:M23"/>
+    <mergeCell ref="N23:R23"/>
+    <mergeCell ref="S23:W23"/>
+    <mergeCell ref="X23:AB23"/>
+    <mergeCell ref="AC23:AG23"/>
+    <mergeCell ref="AH23:AM23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:R22"/>
+    <mergeCell ref="S22:W22"/>
+    <mergeCell ref="X22:AB22"/>
+    <mergeCell ref="AC24:AG24"/>
+    <mergeCell ref="AH24:AM24"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="I25:M25"/>
+    <mergeCell ref="N25:R25"/>
+    <mergeCell ref="S25:W25"/>
+    <mergeCell ref="X25:AB25"/>
+    <mergeCell ref="AC25:AG25"/>
+    <mergeCell ref="AH25:AM25"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="I24:M24"/>
+    <mergeCell ref="N24:R24"/>
+    <mergeCell ref="S24:W24"/>
+    <mergeCell ref="X24:AB24"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -16253,7 +16690,7 @@
     </row>
     <row r="2" spans="1:76">
       <c r="A2" s="24" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
@@ -16290,7 +16727,7 @@
       <c r="AK2" s="25"/>
       <c r="AL2" s="25"/>
       <c r="AM2" s="24" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AQ2" s="21"/>
       <c r="AR2" s="21"/>
@@ -16407,30 +16844,30 @@
       <c r="AK4" s="25"/>
       <c r="AL4" s="25"/>
       <c r="AM4" s="179" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AN4" s="179"/>
       <c r="AO4" s="179"/>
       <c r="AP4" s="179"/>
       <c r="AQ4" s="106" t="s">
+        <v>382</v>
+      </c>
+      <c r="AR4" s="106" t="s">
         <v>383</v>
       </c>
-      <c r="AR4" s="106" t="s">
+      <c r="AS4" s="106" t="s">
         <v>384</v>
       </c>
-      <c r="AS4" s="106" t="s">
+      <c r="AT4" s="106" t="s">
         <v>385</v>
       </c>
-      <c r="AT4" s="106" t="s">
+      <c r="AU4" s="106" t="s">
         <v>386</v>
-      </c>
-      <c r="AU4" s="106" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="5" spans="1:76">
       <c r="A5" s="99" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -16470,27 +16907,27 @@
       <c r="AK5" s="28"/>
       <c r="AL5" s="28"/>
       <c r="AM5" s="146" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AN5" s="147"/>
       <c r="AO5" s="152"/>
       <c r="AP5" s="264" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AQ5" s="266" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AR5" s="266" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AS5" s="266" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AT5" s="266" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AU5" s="266" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:76" ht="13.8" customHeight="1">
@@ -16544,23 +16981,23 @@
     </row>
     <row r="7" spans="1:76" ht="16.2">
       <c r="A7" s="100" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B7" s="100"/>
       <c r="C7" s="100"/>
-      <c r="D7" s="249"/>
-      <c r="E7" s="249"/>
-      <c r="F7" s="249"/>
-      <c r="G7" s="249"/>
-      <c r="H7" s="249"/>
+      <c r="D7" s="246"/>
+      <c r="E7" s="246"/>
+      <c r="F7" s="246"/>
+      <c r="G7" s="246"/>
+      <c r="H7" s="246"/>
       <c r="I7" s="101" t="s">
+        <v>355</v>
+      </c>
+      <c r="J7" s="246"/>
+      <c r="K7" s="246"/>
+      <c r="L7" s="246"/>
+      <c r="M7" s="100" t="s">
         <v>356</v>
-      </c>
-      <c r="J7" s="249"/>
-      <c r="K7" s="249"/>
-      <c r="L7" s="249"/>
-      <c r="M7" s="100" t="s">
-        <v>357</v>
       </c>
       <c r="N7" s="100"/>
       <c r="O7" s="100"/>
@@ -16572,7 +17009,7 @@
       <c r="U7" s="236"/>
       <c r="V7" s="236"/>
       <c r="W7" s="100" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="X7" s="100"/>
       <c r="Y7" s="100"/>
@@ -16592,22 +17029,22 @@
       <c r="AN7" s="158"/>
       <c r="AO7" s="159"/>
       <c r="AP7" s="264" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AQ7" s="266" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AR7" s="266" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AS7" s="266" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AT7" s="266" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AU7" s="266" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:76" ht="13.8" customHeight="1">
@@ -16623,7 +17060,7 @@
       <c r="J8" s="236"/>
       <c r="K8" s="236"/>
       <c r="L8" s="100" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M8" s="236"/>
       <c r="N8" s="236"/>
@@ -16636,12 +17073,12 @@
       <c r="U8" s="100" t="s">
         <v>241</v>
       </c>
-      <c r="V8" s="249"/>
-      <c r="W8" s="249"/>
-      <c r="X8" s="249"/>
-      <c r="Y8" s="249"/>
+      <c r="V8" s="246"/>
+      <c r="W8" s="246"/>
+      <c r="X8" s="246"/>
+      <c r="Y8" s="246"/>
       <c r="Z8" s="100" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA8" s="100"/>
       <c r="AB8" s="100"/>
@@ -16705,32 +17142,32 @@
       <c r="AK9" s="28"/>
       <c r="AL9" s="28"/>
       <c r="AM9" s="146" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AN9" s="147"/>
       <c r="AO9" s="152"/>
       <c r="AP9" s="264" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AQ9" s="266" t="s">
+        <v>390</v>
+      </c>
+      <c r="AR9" s="266" t="s">
         <v>391</v>
       </c>
-      <c r="AR9" s="266" t="s">
+      <c r="AS9" s="266" t="s">
         <v>392</v>
       </c>
-      <c r="AS9" s="266" t="s">
+      <c r="AT9" s="266" t="s">
         <v>393</v>
       </c>
-      <c r="AT9" s="266" t="s">
+      <c r="AU9" s="266" t="s">
         <v>394</v>
-      </c>
-      <c r="AU9" s="266" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:76" ht="16.2" customHeight="1">
       <c r="A10" s="102" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B10" s="100"/>
       <c r="C10" s="100"/>
@@ -16742,18 +17179,18 @@
       <c r="I10" s="236"/>
       <c r="J10" s="236"/>
       <c r="K10" s="100" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L10" s="100"/>
-      <c r="M10" s="249"/>
-      <c r="N10" s="249"/>
-      <c r="O10" s="249"/>
-      <c r="P10" s="249"/>
-      <c r="Q10" s="249"/>
-      <c r="R10" s="249"/>
-      <c r="S10" s="249"/>
-      <c r="T10" s="249"/>
-      <c r="U10" s="249"/>
+      <c r="M10" s="246"/>
+      <c r="N10" s="246"/>
+      <c r="O10" s="246"/>
+      <c r="P10" s="246"/>
+      <c r="Q10" s="246"/>
+      <c r="R10" s="246"/>
+      <c r="S10" s="246"/>
+      <c r="T10" s="246"/>
+      <c r="U10" s="246"/>
       <c r="V10" s="28"/>
       <c r="W10" s="28"/>
       <c r="X10" s="28"/>
@@ -16783,7 +17220,7 @@
     </row>
     <row r="11" spans="1:76">
       <c r="A11" s="99" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B11" s="100"/>
       <c r="C11" s="100"/>
@@ -16826,22 +17263,22 @@
       <c r="AN11" s="158"/>
       <c r="AO11" s="159"/>
       <c r="AP11" s="264" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AQ11" s="266" t="s">
+        <v>390</v>
+      </c>
+      <c r="AR11" s="266" t="s">
         <v>391</v>
       </c>
-      <c r="AR11" s="266" t="s">
+      <c r="AS11" s="266" t="s">
         <v>392</v>
       </c>
-      <c r="AS11" s="266" t="s">
+      <c r="AT11" s="266" t="s">
         <v>393</v>
       </c>
-      <c r="AT11" s="266" t="s">
+      <c r="AU11" s="266" t="s">
         <v>394</v>
-      </c>
-      <c r="AU11" s="266" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:76" ht="13.8" customHeight="1">
@@ -16895,7 +17332,7 @@
     </row>
     <row r="13" spans="1:76" ht="14.4">
       <c r="A13" s="99" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
@@ -16935,32 +17372,32 @@
       <c r="AK13" s="28"/>
       <c r="AL13" s="28"/>
       <c r="AM13" s="146" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AN13" s="147"/>
       <c r="AO13" s="152"/>
       <c r="AP13" s="267" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AQ13" s="266" t="s">
+        <v>399</v>
+      </c>
+      <c r="AR13" s="266" t="s">
         <v>400</v>
       </c>
-      <c r="AR13" s="266" t="s">
+      <c r="AS13" s="266" t="s">
         <v>401</v>
       </c>
-      <c r="AS13" s="266" t="s">
+      <c r="AT13" s="266" t="s">
         <v>402</v>
       </c>
-      <c r="AT13" s="266" t="s">
+      <c r="AU13" s="266" t="s">
         <v>403</v>
-      </c>
-      <c r="AU13" s="266" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:76" ht="18" customHeight="1">
       <c r="A14" s="250" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B14" s="251"/>
       <c r="C14" s="251"/>
@@ -16976,7 +17413,7 @@
       <c r="M14" s="251"/>
       <c r="N14" s="252"/>
       <c r="O14" s="256" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P14" s="257"/>
       <c r="Q14" s="257"/>
@@ -16984,7 +17421,7 @@
       <c r="S14" s="257"/>
       <c r="T14" s="258"/>
       <c r="U14" s="256" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="V14" s="257"/>
       <c r="W14" s="257"/>
@@ -16992,7 +17429,7 @@
       <c r="Y14" s="257"/>
       <c r="Z14" s="258"/>
       <c r="AA14" s="256" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB14" s="257"/>
       <c r="AC14" s="257"/>
@@ -17000,7 +17437,7 @@
       <c r="AE14" s="257"/>
       <c r="AF14" s="258"/>
       <c r="AG14" s="256" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AH14" s="257"/>
       <c r="AI14" s="257"/>
@@ -17060,67 +17497,67 @@
       <c r="AN15" s="158"/>
       <c r="AO15" s="159"/>
       <c r="AP15" s="267" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AQ15" s="266" t="s">
+        <v>399</v>
+      </c>
+      <c r="AR15" s="266" t="s">
         <v>400</v>
       </c>
-      <c r="AR15" s="266" t="s">
+      <c r="AS15" s="266" t="s">
         <v>401</v>
       </c>
-      <c r="AS15" s="266" t="s">
+      <c r="AT15" s="266" t="s">
         <v>402</v>
       </c>
-      <c r="AT15" s="266" t="s">
+      <c r="AU15" s="266" t="s">
         <v>403</v>
       </c>
-      <c r="AU15" s="266" t="s">
-        <v>404</v>
-      </c>
     </row>
     <row r="16" spans="1:76" ht="16.95" customHeight="1">
-      <c r="A16" s="246" t="s">
-        <v>367</v>
-      </c>
-      <c r="B16" s="246"/>
-      <c r="C16" s="246"/>
-      <c r="D16" s="246"/>
-      <c r="E16" s="246"/>
-      <c r="F16" s="246"/>
-      <c r="G16" s="246"/>
-      <c r="H16" s="247" t="s">
-        <v>372</v>
-      </c>
-      <c r="I16" s="247"/>
-      <c r="J16" s="247"/>
-      <c r="K16" s="247"/>
-      <c r="L16" s="247"/>
-      <c r="M16" s="247"/>
-      <c r="N16" s="247"/>
-      <c r="O16" s="248"/>
-      <c r="P16" s="248"/>
-      <c r="Q16" s="248"/>
-      <c r="R16" s="248"/>
-      <c r="S16" s="248"/>
-      <c r="T16" s="248"/>
-      <c r="U16" s="248"/>
-      <c r="V16" s="248"/>
-      <c r="W16" s="248"/>
-      <c r="X16" s="248"/>
-      <c r="Y16" s="248"/>
-      <c r="Z16" s="248"/>
-      <c r="AA16" s="248"/>
-      <c r="AB16" s="248"/>
-      <c r="AC16" s="248"/>
-      <c r="AD16" s="248"/>
-      <c r="AE16" s="248"/>
-      <c r="AF16" s="248"/>
-      <c r="AG16" s="248"/>
-      <c r="AH16" s="248"/>
-      <c r="AI16" s="248"/>
-      <c r="AJ16" s="248"/>
-      <c r="AK16" s="248"/>
-      <c r="AL16" s="248"/>
+      <c r="A16" s="247" t="s">
+        <v>366</v>
+      </c>
+      <c r="B16" s="247"/>
+      <c r="C16" s="247"/>
+      <c r="D16" s="247"/>
+      <c r="E16" s="247"/>
+      <c r="F16" s="247"/>
+      <c r="G16" s="247"/>
+      <c r="H16" s="248" t="s">
+        <v>371</v>
+      </c>
+      <c r="I16" s="248"/>
+      <c r="J16" s="248"/>
+      <c r="K16" s="248"/>
+      <c r="L16" s="248"/>
+      <c r="M16" s="248"/>
+      <c r="N16" s="248"/>
+      <c r="O16" s="249"/>
+      <c r="P16" s="249"/>
+      <c r="Q16" s="249"/>
+      <c r="R16" s="249"/>
+      <c r="S16" s="249"/>
+      <c r="T16" s="249"/>
+      <c r="U16" s="249"/>
+      <c r="V16" s="249"/>
+      <c r="W16" s="249"/>
+      <c r="X16" s="249"/>
+      <c r="Y16" s="249"/>
+      <c r="Z16" s="249"/>
+      <c r="AA16" s="249"/>
+      <c r="AB16" s="249"/>
+      <c r="AC16" s="249"/>
+      <c r="AD16" s="249"/>
+      <c r="AE16" s="249"/>
+      <c r="AF16" s="249"/>
+      <c r="AG16" s="249"/>
+      <c r="AH16" s="249"/>
+      <c r="AI16" s="249"/>
+      <c r="AJ16" s="249"/>
+      <c r="AK16" s="249"/>
+      <c r="AL16" s="249"/>
       <c r="AM16" s="148"/>
       <c r="AN16" s="149"/>
       <c r="AO16" s="153"/>
@@ -17132,109 +17569,109 @@
       <c r="AU16" s="266"/>
     </row>
     <row r="17" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A17" s="246"/>
-      <c r="B17" s="246"/>
-      <c r="C17" s="246"/>
-      <c r="D17" s="246"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="247"/>
-      <c r="I17" s="247"/>
-      <c r="J17" s="247"/>
-      <c r="K17" s="247"/>
-      <c r="L17" s="247"/>
-      <c r="M17" s="247"/>
-      <c r="N17" s="247"/>
-      <c r="O17" s="248"/>
-      <c r="P17" s="248"/>
-      <c r="Q17" s="248"/>
-      <c r="R17" s="248"/>
-      <c r="S17" s="248"/>
-      <c r="T17" s="248"/>
-      <c r="U17" s="248"/>
-      <c r="V17" s="248"/>
-      <c r="W17" s="248"/>
-      <c r="X17" s="248"/>
-      <c r="Y17" s="248"/>
-      <c r="Z17" s="248"/>
-      <c r="AA17" s="248"/>
-      <c r="AB17" s="248"/>
-      <c r="AC17" s="248"/>
-      <c r="AD17" s="248"/>
-      <c r="AE17" s="248"/>
-      <c r="AF17" s="248"/>
-      <c r="AG17" s="248"/>
-      <c r="AH17" s="248"/>
-      <c r="AI17" s="248"/>
-      <c r="AJ17" s="248"/>
-      <c r="AK17" s="248"/>
-      <c r="AL17" s="248"/>
+      <c r="A17" s="247"/>
+      <c r="B17" s="247"/>
+      <c r="C17" s="247"/>
+      <c r="D17" s="247"/>
+      <c r="E17" s="247"/>
+      <c r="F17" s="247"/>
+      <c r="G17" s="247"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="248"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="248"/>
+      <c r="M17" s="248"/>
+      <c r="N17" s="248"/>
+      <c r="O17" s="249"/>
+      <c r="P17" s="249"/>
+      <c r="Q17" s="249"/>
+      <c r="R17" s="249"/>
+      <c r="S17" s="249"/>
+      <c r="T17" s="249"/>
+      <c r="U17" s="249"/>
+      <c r="V17" s="249"/>
+      <c r="W17" s="249"/>
+      <c r="X17" s="249"/>
+      <c r="Y17" s="249"/>
+      <c r="Z17" s="249"/>
+      <c r="AA17" s="249"/>
+      <c r="AB17" s="249"/>
+      <c r="AC17" s="249"/>
+      <c r="AD17" s="249"/>
+      <c r="AE17" s="249"/>
+      <c r="AF17" s="249"/>
+      <c r="AG17" s="249"/>
+      <c r="AH17" s="249"/>
+      <c r="AI17" s="249"/>
+      <c r="AJ17" s="249"/>
+      <c r="AK17" s="249"/>
+      <c r="AL17" s="249"/>
       <c r="AM17" s="146" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AN17" s="147"/>
       <c r="AO17" s="152"/>
       <c r="AP17" s="267" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AQ17" s="266" t="s">
+        <v>404</v>
+      </c>
+      <c r="AR17" s="266" t="s">
         <v>405</v>
       </c>
-      <c r="AR17" s="266" t="s">
+      <c r="AS17" s="266" t="s">
         <v>406</v>
       </c>
-      <c r="AS17" s="266" t="s">
+      <c r="AT17" s="266" t="s">
         <v>407</v>
       </c>
-      <c r="AT17" s="266" t="s">
+      <c r="AU17" s="266" t="s">
         <v>408</v>
       </c>
-      <c r="AU17" s="266" t="s">
-        <v>409</v>
-      </c>
     </row>
     <row r="18" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A18" s="246"/>
-      <c r="B18" s="246"/>
-      <c r="C18" s="246"/>
-      <c r="D18" s="246"/>
-      <c r="E18" s="246"/>
-      <c r="F18" s="246"/>
-      <c r="G18" s="246"/>
-      <c r="H18" s="247" t="s">
-        <v>373</v>
-      </c>
-      <c r="I18" s="247"/>
-      <c r="J18" s="247"/>
-      <c r="K18" s="247"/>
-      <c r="L18" s="247"/>
-      <c r="M18" s="247"/>
-      <c r="N18" s="247"/>
-      <c r="O18" s="248"/>
-      <c r="P18" s="248"/>
-      <c r="Q18" s="248"/>
-      <c r="R18" s="248"/>
-      <c r="S18" s="248"/>
-      <c r="T18" s="248"/>
-      <c r="U18" s="248"/>
-      <c r="V18" s="248"/>
-      <c r="W18" s="248"/>
-      <c r="X18" s="248"/>
-      <c r="Y18" s="248"/>
-      <c r="Z18" s="248"/>
-      <c r="AA18" s="248"/>
-      <c r="AB18" s="248"/>
-      <c r="AC18" s="248"/>
-      <c r="AD18" s="248"/>
-      <c r="AE18" s="248"/>
-      <c r="AF18" s="248"/>
-      <c r="AG18" s="248"/>
-      <c r="AH18" s="248"/>
-      <c r="AI18" s="248"/>
-      <c r="AJ18" s="248"/>
-      <c r="AK18" s="248"/>
-      <c r="AL18" s="248"/>
+      <c r="A18" s="247"/>
+      <c r="B18" s="247"/>
+      <c r="C18" s="247"/>
+      <c r="D18" s="247"/>
+      <c r="E18" s="247"/>
+      <c r="F18" s="247"/>
+      <c r="G18" s="247"/>
+      <c r="H18" s="248" t="s">
+        <v>372</v>
+      </c>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
+      <c r="M18" s="248"/>
+      <c r="N18" s="248"/>
+      <c r="O18" s="249"/>
+      <c r="P18" s="249"/>
+      <c r="Q18" s="249"/>
+      <c r="R18" s="249"/>
+      <c r="S18" s="249"/>
+      <c r="T18" s="249"/>
+      <c r="U18" s="249"/>
+      <c r="V18" s="249"/>
+      <c r="W18" s="249"/>
+      <c r="X18" s="249"/>
+      <c r="Y18" s="249"/>
+      <c r="Z18" s="249"/>
+      <c r="AA18" s="249"/>
+      <c r="AB18" s="249"/>
+      <c r="AC18" s="249"/>
+      <c r="AD18" s="249"/>
+      <c r="AE18" s="249"/>
+      <c r="AF18" s="249"/>
+      <c r="AG18" s="249"/>
+      <c r="AH18" s="249"/>
+      <c r="AI18" s="249"/>
+      <c r="AJ18" s="249"/>
+      <c r="AK18" s="249"/>
+      <c r="AL18" s="249"/>
       <c r="AM18" s="157"/>
       <c r="AN18" s="158"/>
       <c r="AO18" s="159"/>
@@ -17246,109 +17683,109 @@
       <c r="AU18" s="266"/>
     </row>
     <row r="19" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A19" s="246"/>
-      <c r="B19" s="246"/>
-      <c r="C19" s="246"/>
-      <c r="D19" s="246"/>
-      <c r="E19" s="246"/>
-      <c r="F19" s="246"/>
-      <c r="G19" s="246"/>
-      <c r="H19" s="247"/>
-      <c r="I19" s="247"/>
-      <c r="J19" s="247"/>
-      <c r="K19" s="247"/>
-      <c r="L19" s="247"/>
-      <c r="M19" s="247"/>
-      <c r="N19" s="247"/>
-      <c r="O19" s="248"/>
-      <c r="P19" s="248"/>
-      <c r="Q19" s="248"/>
-      <c r="R19" s="248"/>
-      <c r="S19" s="248"/>
-      <c r="T19" s="248"/>
-      <c r="U19" s="248"/>
-      <c r="V19" s="248"/>
-      <c r="W19" s="248"/>
-      <c r="X19" s="248"/>
-      <c r="Y19" s="248"/>
-      <c r="Z19" s="248"/>
-      <c r="AA19" s="248"/>
-      <c r="AB19" s="248"/>
-      <c r="AC19" s="248"/>
-      <c r="AD19" s="248"/>
-      <c r="AE19" s="248"/>
-      <c r="AF19" s="248"/>
-      <c r="AG19" s="248"/>
-      <c r="AH19" s="248"/>
-      <c r="AI19" s="248"/>
-      <c r="AJ19" s="248"/>
-      <c r="AK19" s="248"/>
-      <c r="AL19" s="248"/>
+      <c r="A19" s="247"/>
+      <c r="B19" s="247"/>
+      <c r="C19" s="247"/>
+      <c r="D19" s="247"/>
+      <c r="E19" s="247"/>
+      <c r="F19" s="247"/>
+      <c r="G19" s="247"/>
+      <c r="H19" s="248"/>
+      <c r="I19" s="248"/>
+      <c r="J19" s="248"/>
+      <c r="K19" s="248"/>
+      <c r="L19" s="248"/>
+      <c r="M19" s="248"/>
+      <c r="N19" s="248"/>
+      <c r="O19" s="249"/>
+      <c r="P19" s="249"/>
+      <c r="Q19" s="249"/>
+      <c r="R19" s="249"/>
+      <c r="S19" s="249"/>
+      <c r="T19" s="249"/>
+      <c r="U19" s="249"/>
+      <c r="V19" s="249"/>
+      <c r="W19" s="249"/>
+      <c r="X19" s="249"/>
+      <c r="Y19" s="249"/>
+      <c r="Z19" s="249"/>
+      <c r="AA19" s="249"/>
+      <c r="AB19" s="249"/>
+      <c r="AC19" s="249"/>
+      <c r="AD19" s="249"/>
+      <c r="AE19" s="249"/>
+      <c r="AF19" s="249"/>
+      <c r="AG19" s="249"/>
+      <c r="AH19" s="249"/>
+      <c r="AI19" s="249"/>
+      <c r="AJ19" s="249"/>
+      <c r="AK19" s="249"/>
+      <c r="AL19" s="249"/>
       <c r="AM19" s="157"/>
       <c r="AN19" s="158"/>
       <c r="AO19" s="159"/>
       <c r="AP19" s="267" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AQ19" s="266" t="s">
+        <v>404</v>
+      </c>
+      <c r="AR19" s="266" t="s">
         <v>405</v>
       </c>
-      <c r="AR19" s="266" t="s">
+      <c r="AS19" s="266" t="s">
         <v>406</v>
       </c>
-      <c r="AS19" s="266" t="s">
+      <c r="AT19" s="266" t="s">
         <v>407</v>
       </c>
-      <c r="AT19" s="266" t="s">
+      <c r="AU19" s="266" t="s">
         <v>408</v>
       </c>
-      <c r="AU19" s="266" t="s">
-        <v>409</v>
-      </c>
     </row>
     <row r="20" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A20" s="247" t="s">
-        <v>368</v>
-      </c>
-      <c r="B20" s="247"/>
-      <c r="C20" s="247"/>
-      <c r="D20" s="247"/>
-      <c r="E20" s="247"/>
-      <c r="F20" s="247"/>
-      <c r="G20" s="247"/>
-      <c r="H20" s="247" t="s">
-        <v>374</v>
-      </c>
-      <c r="I20" s="247"/>
-      <c r="J20" s="247"/>
-      <c r="K20" s="247"/>
-      <c r="L20" s="247"/>
-      <c r="M20" s="247"/>
-      <c r="N20" s="247"/>
-      <c r="O20" s="248"/>
-      <c r="P20" s="248"/>
-      <c r="Q20" s="248"/>
-      <c r="R20" s="248"/>
-      <c r="S20" s="248"/>
-      <c r="T20" s="248"/>
-      <c r="U20" s="248"/>
-      <c r="V20" s="248"/>
-      <c r="W20" s="248"/>
-      <c r="X20" s="248"/>
-      <c r="Y20" s="248"/>
-      <c r="Z20" s="248"/>
-      <c r="AA20" s="248"/>
-      <c r="AB20" s="248"/>
-      <c r="AC20" s="248"/>
-      <c r="AD20" s="248"/>
-      <c r="AE20" s="248"/>
-      <c r="AF20" s="248"/>
-      <c r="AG20" s="248"/>
-      <c r="AH20" s="248"/>
-      <c r="AI20" s="248"/>
-      <c r="AJ20" s="248"/>
-      <c r="AK20" s="248"/>
-      <c r="AL20" s="248"/>
+      <c r="A20" s="248" t="s">
+        <v>367</v>
+      </c>
+      <c r="B20" s="248"/>
+      <c r="C20" s="248"/>
+      <c r="D20" s="248"/>
+      <c r="E20" s="248"/>
+      <c r="F20" s="248"/>
+      <c r="G20" s="248"/>
+      <c r="H20" s="248" t="s">
+        <v>373</v>
+      </c>
+      <c r="I20" s="248"/>
+      <c r="J20" s="248"/>
+      <c r="K20" s="248"/>
+      <c r="L20" s="248"/>
+      <c r="M20" s="248"/>
+      <c r="N20" s="248"/>
+      <c r="O20" s="249"/>
+      <c r="P20" s="249"/>
+      <c r="Q20" s="249"/>
+      <c r="R20" s="249"/>
+      <c r="S20" s="249"/>
+      <c r="T20" s="249"/>
+      <c r="U20" s="249"/>
+      <c r="V20" s="249"/>
+      <c r="W20" s="249"/>
+      <c r="X20" s="249"/>
+      <c r="Y20" s="249"/>
+      <c r="Z20" s="249"/>
+      <c r="AA20" s="249"/>
+      <c r="AB20" s="249"/>
+      <c r="AC20" s="249"/>
+      <c r="AD20" s="249"/>
+      <c r="AE20" s="249"/>
+      <c r="AF20" s="249"/>
+      <c r="AG20" s="249"/>
+      <c r="AH20" s="249"/>
+      <c r="AI20" s="249"/>
+      <c r="AJ20" s="249"/>
+      <c r="AK20" s="249"/>
+      <c r="AL20" s="249"/>
       <c r="AM20" s="148"/>
       <c r="AN20" s="149"/>
       <c r="AO20" s="153"/>
@@ -17360,107 +17797,107 @@
       <c r="AU20" s="266"/>
     </row>
     <row r="21" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A21" s="247"/>
-      <c r="B21" s="247"/>
-      <c r="C21" s="247"/>
-      <c r="D21" s="247"/>
-      <c r="E21" s="247"/>
-      <c r="F21" s="247"/>
-      <c r="G21" s="247"/>
-      <c r="H21" s="247"/>
-      <c r="I21" s="247"/>
-      <c r="J21" s="247"/>
-      <c r="K21" s="247"/>
-      <c r="L21" s="247"/>
-      <c r="M21" s="247"/>
-      <c r="N21" s="247"/>
-      <c r="O21" s="248"/>
-      <c r="P21" s="248"/>
-      <c r="Q21" s="248"/>
-      <c r="R21" s="248"/>
-      <c r="S21" s="248"/>
-      <c r="T21" s="248"/>
-      <c r="U21" s="248"/>
-      <c r="V21" s="248"/>
-      <c r="W21" s="248"/>
-      <c r="X21" s="248"/>
-      <c r="Y21" s="248"/>
-      <c r="Z21" s="248"/>
-      <c r="AA21" s="248"/>
-      <c r="AB21" s="248"/>
-      <c r="AC21" s="248"/>
-      <c r="AD21" s="248"/>
-      <c r="AE21" s="248"/>
-      <c r="AF21" s="248"/>
-      <c r="AG21" s="248"/>
-      <c r="AH21" s="248"/>
-      <c r="AI21" s="248"/>
-      <c r="AJ21" s="248"/>
-      <c r="AK21" s="248"/>
-      <c r="AL21" s="248"/>
+      <c r="A21" s="248"/>
+      <c r="B21" s="248"/>
+      <c r="C21" s="248"/>
+      <c r="D21" s="248"/>
+      <c r="E21" s="248"/>
+      <c r="F21" s="248"/>
+      <c r="G21" s="248"/>
+      <c r="H21" s="248"/>
+      <c r="I21" s="248"/>
+      <c r="J21" s="248"/>
+      <c r="K21" s="248"/>
+      <c r="L21" s="248"/>
+      <c r="M21" s="248"/>
+      <c r="N21" s="248"/>
+      <c r="O21" s="249"/>
+      <c r="P21" s="249"/>
+      <c r="Q21" s="249"/>
+      <c r="R21" s="249"/>
+      <c r="S21" s="249"/>
+      <c r="T21" s="249"/>
+      <c r="U21" s="249"/>
+      <c r="V21" s="249"/>
+      <c r="W21" s="249"/>
+      <c r="X21" s="249"/>
+      <c r="Y21" s="249"/>
+      <c r="Z21" s="249"/>
+      <c r="AA21" s="249"/>
+      <c r="AB21" s="249"/>
+      <c r="AC21" s="249"/>
+      <c r="AD21" s="249"/>
+      <c r="AE21" s="249"/>
+      <c r="AF21" s="249"/>
+      <c r="AG21" s="249"/>
+      <c r="AH21" s="249"/>
+      <c r="AI21" s="249"/>
+      <c r="AJ21" s="249"/>
+      <c r="AK21" s="249"/>
+      <c r="AL21" s="249"/>
       <c r="AM21" s="234" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AN21" s="234"/>
       <c r="AO21" s="234"/>
       <c r="AP21" s="234"/>
       <c r="AQ21" s="266" t="s">
+        <v>415</v>
+      </c>
+      <c r="AR21" s="268" t="s">
         <v>416</v>
       </c>
-      <c r="AR21" s="268" t="s">
+      <c r="AS21" s="266" t="s">
         <v>417</v>
       </c>
-      <c r="AS21" s="266" t="s">
+      <c r="AT21" s="266" t="s">
         <v>418</v>
       </c>
-      <c r="AT21" s="266" t="s">
+      <c r="AU21" s="266" t="s">
         <v>419</v>
       </c>
-      <c r="AU21" s="266" t="s">
-        <v>420</v>
-      </c>
     </row>
     <row r="22" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A22" s="247"/>
-      <c r="B22" s="247"/>
-      <c r="C22" s="247"/>
-      <c r="D22" s="247"/>
-      <c r="E22" s="247"/>
-      <c r="F22" s="247"/>
-      <c r="G22" s="247"/>
-      <c r="H22" s="247" t="s">
-        <v>375</v>
-      </c>
-      <c r="I22" s="247"/>
-      <c r="J22" s="247"/>
-      <c r="K22" s="247"/>
-      <c r="L22" s="247"/>
-      <c r="M22" s="247"/>
-      <c r="N22" s="247"/>
-      <c r="O22" s="248"/>
-      <c r="P22" s="248"/>
-      <c r="Q22" s="248"/>
-      <c r="R22" s="248"/>
-      <c r="S22" s="248"/>
-      <c r="T22" s="248"/>
-      <c r="U22" s="248"/>
-      <c r="V22" s="248"/>
-      <c r="W22" s="248"/>
-      <c r="X22" s="248"/>
-      <c r="Y22" s="248"/>
-      <c r="Z22" s="248"/>
-      <c r="AA22" s="248"/>
-      <c r="AB22" s="248"/>
-      <c r="AC22" s="248"/>
-      <c r="AD22" s="248"/>
-      <c r="AE22" s="248"/>
-      <c r="AF22" s="248"/>
-      <c r="AG22" s="248"/>
-      <c r="AH22" s="248"/>
-      <c r="AI22" s="248"/>
-      <c r="AJ22" s="248"/>
-      <c r="AK22" s="248"/>
-      <c r="AL22" s="248"/>
+      <c r="A22" s="248"/>
+      <c r="B22" s="248"/>
+      <c r="C22" s="248"/>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="248"/>
+      <c r="G22" s="248"/>
+      <c r="H22" s="248" t="s">
+        <v>374</v>
+      </c>
+      <c r="I22" s="248"/>
+      <c r="J22" s="248"/>
+      <c r="K22" s="248"/>
+      <c r="L22" s="248"/>
+      <c r="M22" s="248"/>
+      <c r="N22" s="248"/>
+      <c r="O22" s="249"/>
+      <c r="P22" s="249"/>
+      <c r="Q22" s="249"/>
+      <c r="R22" s="249"/>
+      <c r="S22" s="249"/>
+      <c r="T22" s="249"/>
+      <c r="U22" s="249"/>
+      <c r="V22" s="249"/>
+      <c r="W22" s="249"/>
+      <c r="X22" s="249"/>
+      <c r="Y22" s="249"/>
+      <c r="Z22" s="249"/>
+      <c r="AA22" s="249"/>
+      <c r="AB22" s="249"/>
+      <c r="AC22" s="249"/>
+      <c r="AD22" s="249"/>
+      <c r="AE22" s="249"/>
+      <c r="AF22" s="249"/>
+      <c r="AG22" s="249"/>
+      <c r="AH22" s="249"/>
+      <c r="AI22" s="249"/>
+      <c r="AJ22" s="249"/>
+      <c r="AK22" s="249"/>
+      <c r="AL22" s="249"/>
       <c r="AM22" s="234"/>
       <c r="AN22" s="234"/>
       <c r="AO22" s="234"/>
@@ -17472,109 +17909,109 @@
       <c r="AU22" s="266"/>
     </row>
     <row r="23" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A23" s="247"/>
-      <c r="B23" s="247"/>
-      <c r="C23" s="247"/>
-      <c r="D23" s="247"/>
-      <c r="E23" s="247"/>
-      <c r="F23" s="247"/>
-      <c r="G23" s="247"/>
-      <c r="H23" s="247"/>
-      <c r="I23" s="247"/>
-      <c r="J23" s="247"/>
-      <c r="K23" s="247"/>
-      <c r="L23" s="247"/>
-      <c r="M23" s="247"/>
-      <c r="N23" s="247"/>
-      <c r="O23" s="248"/>
-      <c r="P23" s="248"/>
-      <c r="Q23" s="248"/>
-      <c r="R23" s="248"/>
-      <c r="S23" s="248"/>
-      <c r="T23" s="248"/>
-      <c r="U23" s="248"/>
-      <c r="V23" s="248"/>
-      <c r="W23" s="248"/>
-      <c r="X23" s="248"/>
-      <c r="Y23" s="248"/>
-      <c r="Z23" s="248"/>
-      <c r="AA23" s="248"/>
-      <c r="AB23" s="248"/>
-      <c r="AC23" s="248"/>
-      <c r="AD23" s="248"/>
-      <c r="AE23" s="248"/>
-      <c r="AF23" s="248"/>
-      <c r="AG23" s="248"/>
-      <c r="AH23" s="248"/>
-      <c r="AI23" s="248"/>
-      <c r="AJ23" s="248"/>
-      <c r="AK23" s="248"/>
-      <c r="AL23" s="248"/>
+      <c r="A23" s="248"/>
+      <c r="B23" s="248"/>
+      <c r="C23" s="248"/>
+      <c r="D23" s="248"/>
+      <c r="E23" s="248"/>
+      <c r="F23" s="248"/>
+      <c r="G23" s="248"/>
+      <c r="H23" s="248"/>
+      <c r="I23" s="248"/>
+      <c r="J23" s="248"/>
+      <c r="K23" s="248"/>
+      <c r="L23" s="248"/>
+      <c r="M23" s="248"/>
+      <c r="N23" s="248"/>
+      <c r="O23" s="249"/>
+      <c r="P23" s="249"/>
+      <c r="Q23" s="249"/>
+      <c r="R23" s="249"/>
+      <c r="S23" s="249"/>
+      <c r="T23" s="249"/>
+      <c r="U23" s="249"/>
+      <c r="V23" s="249"/>
+      <c r="W23" s="249"/>
+      <c r="X23" s="249"/>
+      <c r="Y23" s="249"/>
+      <c r="Z23" s="249"/>
+      <c r="AA23" s="249"/>
+      <c r="AB23" s="249"/>
+      <c r="AC23" s="249"/>
+      <c r="AD23" s="249"/>
+      <c r="AE23" s="249"/>
+      <c r="AF23" s="249"/>
+      <c r="AG23" s="249"/>
+      <c r="AH23" s="249"/>
+      <c r="AI23" s="249"/>
+      <c r="AJ23" s="249"/>
+      <c r="AK23" s="249"/>
+      <c r="AL23" s="249"/>
       <c r="AM23" s="234" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN23" s="234"/>
       <c r="AO23" s="234"/>
       <c r="AP23" s="234"/>
       <c r="AQ23" s="266" t="s">
+        <v>410</v>
+      </c>
+      <c r="AR23" s="266" t="s">
         <v>411</v>
       </c>
-      <c r="AR23" s="266" t="s">
+      <c r="AS23" s="266" t="s">
         <v>412</v>
       </c>
-      <c r="AS23" s="266" t="s">
+      <c r="AT23" s="266" t="s">
         <v>413</v>
       </c>
-      <c r="AT23" s="266" t="s">
+      <c r="AU23" s="266" t="s">
         <v>414</v>
       </c>
-      <c r="AU23" s="266" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="24" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A24" s="247" t="s">
-        <v>369</v>
-      </c>
-      <c r="B24" s="247"/>
-      <c r="C24" s="247"/>
-      <c r="D24" s="247"/>
-      <c r="E24" s="247"/>
-      <c r="F24" s="247"/>
-      <c r="G24" s="247"/>
-      <c r="H24" s="247" t="s">
-        <v>376</v>
-      </c>
-      <c r="I24" s="247"/>
-      <c r="J24" s="247"/>
-      <c r="K24" s="247"/>
-      <c r="L24" s="247"/>
-      <c r="M24" s="247"/>
-      <c r="N24" s="247"/>
-      <c r="O24" s="248"/>
-      <c r="P24" s="248"/>
-      <c r="Q24" s="248"/>
-      <c r="R24" s="248"/>
-      <c r="S24" s="248"/>
-      <c r="T24" s="248"/>
-      <c r="U24" s="248"/>
-      <c r="V24" s="248"/>
-      <c r="W24" s="248"/>
-      <c r="X24" s="248"/>
-      <c r="Y24" s="248"/>
-      <c r="Z24" s="248"/>
-      <c r="AA24" s="248"/>
-      <c r="AB24" s="248"/>
-      <c r="AC24" s="248"/>
-      <c r="AD24" s="248"/>
-      <c r="AE24" s="248"/>
-      <c r="AF24" s="248"/>
-      <c r="AG24" s="248"/>
-      <c r="AH24" s="248"/>
-      <c r="AI24" s="248"/>
-      <c r="AJ24" s="248"/>
-      <c r="AK24" s="248"/>
-      <c r="AL24" s="248"/>
+      <c r="A24" s="248" t="s">
+        <v>368</v>
+      </c>
+      <c r="B24" s="248"/>
+      <c r="C24" s="248"/>
+      <c r="D24" s="248"/>
+      <c r="E24" s="248"/>
+      <c r="F24" s="248"/>
+      <c r="G24" s="248"/>
+      <c r="H24" s="248" t="s">
+        <v>375</v>
+      </c>
+      <c r="I24" s="248"/>
+      <c r="J24" s="248"/>
+      <c r="K24" s="248"/>
+      <c r="L24" s="248"/>
+      <c r="M24" s="248"/>
+      <c r="N24" s="248"/>
+      <c r="O24" s="249"/>
+      <c r="P24" s="249"/>
+      <c r="Q24" s="249"/>
+      <c r="R24" s="249"/>
+      <c r="S24" s="249"/>
+      <c r="T24" s="249"/>
+      <c r="U24" s="249"/>
+      <c r="V24" s="249"/>
+      <c r="W24" s="249"/>
+      <c r="X24" s="249"/>
+      <c r="Y24" s="249"/>
+      <c r="Z24" s="249"/>
+      <c r="AA24" s="249"/>
+      <c r="AB24" s="249"/>
+      <c r="AC24" s="249"/>
+      <c r="AD24" s="249"/>
+      <c r="AE24" s="249"/>
+      <c r="AF24" s="249"/>
+      <c r="AG24" s="249"/>
+      <c r="AH24" s="249"/>
+      <c r="AI24" s="249"/>
+      <c r="AJ24" s="249"/>
+      <c r="AK24" s="249"/>
+      <c r="AL24" s="249"/>
       <c r="AM24" s="234"/>
       <c r="AN24" s="234"/>
       <c r="AO24" s="234"/>
@@ -17586,456 +18023,456 @@
       <c r="AU24" s="266"/>
     </row>
     <row r="25" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A25" s="247"/>
-      <c r="B25" s="247"/>
-      <c r="C25" s="247"/>
-      <c r="D25" s="247"/>
-      <c r="E25" s="247"/>
-      <c r="F25" s="247"/>
-      <c r="G25" s="247"/>
-      <c r="H25" s="247"/>
-      <c r="I25" s="247"/>
-      <c r="J25" s="247"/>
-      <c r="K25" s="247"/>
-      <c r="L25" s="247"/>
-      <c r="M25" s="247"/>
-      <c r="N25" s="247"/>
-      <c r="O25" s="248"/>
-      <c r="P25" s="248"/>
-      <c r="Q25" s="248"/>
-      <c r="R25" s="248"/>
-      <c r="S25" s="248"/>
-      <c r="T25" s="248"/>
-      <c r="U25" s="248"/>
-      <c r="V25" s="248"/>
-      <c r="W25" s="248"/>
-      <c r="X25" s="248"/>
-      <c r="Y25" s="248"/>
-      <c r="Z25" s="248"/>
-      <c r="AA25" s="248"/>
-      <c r="AB25" s="248"/>
-      <c r="AC25" s="248"/>
-      <c r="AD25" s="248"/>
-      <c r="AE25" s="248"/>
-      <c r="AF25" s="248"/>
-      <c r="AG25" s="248"/>
-      <c r="AH25" s="248"/>
-      <c r="AI25" s="248"/>
-      <c r="AJ25" s="248"/>
-      <c r="AK25" s="248"/>
-      <c r="AL25" s="248"/>
+      <c r="A25" s="248"/>
+      <c r="B25" s="248"/>
+      <c r="C25" s="248"/>
+      <c r="D25" s="248"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="248"/>
+      <c r="I25" s="248"/>
+      <c r="J25" s="248"/>
+      <c r="K25" s="248"/>
+      <c r="L25" s="248"/>
+      <c r="M25" s="248"/>
+      <c r="N25" s="248"/>
+      <c r="O25" s="249"/>
+      <c r="P25" s="249"/>
+      <c r="Q25" s="249"/>
+      <c r="R25" s="249"/>
+      <c r="S25" s="249"/>
+      <c r="T25" s="249"/>
+      <c r="U25" s="249"/>
+      <c r="V25" s="249"/>
+      <c r="W25" s="249"/>
+      <c r="X25" s="249"/>
+      <c r="Y25" s="249"/>
+      <c r="Z25" s="249"/>
+      <c r="AA25" s="249"/>
+      <c r="AB25" s="249"/>
+      <c r="AC25" s="249"/>
+      <c r="AD25" s="249"/>
+      <c r="AE25" s="249"/>
+      <c r="AF25" s="249"/>
+      <c r="AG25" s="249"/>
+      <c r="AH25" s="249"/>
+      <c r="AI25" s="249"/>
+      <c r="AJ25" s="249"/>
+      <c r="AK25" s="249"/>
+      <c r="AL25" s="249"/>
     </row>
     <row r="26" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A26" s="247"/>
-      <c r="B26" s="247"/>
-      <c r="C26" s="247"/>
-      <c r="D26" s="247"/>
-      <c r="E26" s="247"/>
-      <c r="F26" s="247"/>
-      <c r="G26" s="247"/>
-      <c r="H26" s="247" t="s">
+      <c r="A26" s="248"/>
+      <c r="B26" s="248"/>
+      <c r="C26" s="248"/>
+      <c r="D26" s="248"/>
+      <c r="E26" s="248"/>
+      <c r="F26" s="248"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="248" t="s">
+        <v>376</v>
+      </c>
+      <c r="I26" s="248"/>
+      <c r="J26" s="248"/>
+      <c r="K26" s="248"/>
+      <c r="L26" s="248"/>
+      <c r="M26" s="248"/>
+      <c r="N26" s="248"/>
+      <c r="O26" s="249"/>
+      <c r="P26" s="249"/>
+      <c r="Q26" s="249"/>
+      <c r="R26" s="249"/>
+      <c r="S26" s="249"/>
+      <c r="T26" s="249"/>
+      <c r="U26" s="249"/>
+      <c r="V26" s="249"/>
+      <c r="W26" s="249"/>
+      <c r="X26" s="249"/>
+      <c r="Y26" s="249"/>
+      <c r="Z26" s="249"/>
+      <c r="AA26" s="249"/>
+      <c r="AB26" s="249"/>
+      <c r="AC26" s="249"/>
+      <c r="AD26" s="249"/>
+      <c r="AE26" s="249"/>
+      <c r="AF26" s="249"/>
+      <c r="AG26" s="249"/>
+      <c r="AH26" s="249"/>
+      <c r="AI26" s="249"/>
+      <c r="AJ26" s="249"/>
+      <c r="AK26" s="249"/>
+      <c r="AL26" s="249"/>
+    </row>
+    <row r="27" spans="1:47" ht="16.95" customHeight="1">
+      <c r="A27" s="248"/>
+      <c r="B27" s="248"/>
+      <c r="C27" s="248"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="248"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="248"/>
+      <c r="I27" s="248"/>
+      <c r="J27" s="248"/>
+      <c r="K27" s="248"/>
+      <c r="L27" s="248"/>
+      <c r="M27" s="248"/>
+      <c r="N27" s="248"/>
+      <c r="O27" s="249"/>
+      <c r="P27" s="249"/>
+      <c r="Q27" s="249"/>
+      <c r="R27" s="249"/>
+      <c r="S27" s="249"/>
+      <c r="T27" s="249"/>
+      <c r="U27" s="249"/>
+      <c r="V27" s="249"/>
+      <c r="W27" s="249"/>
+      <c r="X27" s="249"/>
+      <c r="Y27" s="249"/>
+      <c r="Z27" s="249"/>
+      <c r="AA27" s="249"/>
+      <c r="AB27" s="249"/>
+      <c r="AC27" s="249"/>
+      <c r="AD27" s="249"/>
+      <c r="AE27" s="249"/>
+      <c r="AF27" s="249"/>
+      <c r="AG27" s="249"/>
+      <c r="AH27" s="249"/>
+      <c r="AI27" s="249"/>
+      <c r="AJ27" s="249"/>
+      <c r="AK27" s="249"/>
+      <c r="AL27" s="249"/>
+    </row>
+    <row r="28" spans="1:47" ht="16.95" customHeight="1">
+      <c r="A28" s="248" t="s">
+        <v>369</v>
+      </c>
+      <c r="B28" s="248"/>
+      <c r="C28" s="248"/>
+      <c r="D28" s="248"/>
+      <c r="E28" s="248"/>
+      <c r="F28" s="248"/>
+      <c r="G28" s="248"/>
+      <c r="H28" s="248" t="s">
         <v>377</v>
       </c>
-      <c r="I26" s="247"/>
-      <c r="J26" s="247"/>
-      <c r="K26" s="247"/>
-      <c r="L26" s="247"/>
-      <c r="M26" s="247"/>
-      <c r="N26" s="247"/>
-      <c r="O26" s="248"/>
-      <c r="P26" s="248"/>
-      <c r="Q26" s="248"/>
-      <c r="R26" s="248"/>
-      <c r="S26" s="248"/>
-      <c r="T26" s="248"/>
-      <c r="U26" s="248"/>
-      <c r="V26" s="248"/>
-      <c r="W26" s="248"/>
-      <c r="X26" s="248"/>
-      <c r="Y26" s="248"/>
-      <c r="Z26" s="248"/>
-      <c r="AA26" s="248"/>
-      <c r="AB26" s="248"/>
-      <c r="AC26" s="248"/>
-      <c r="AD26" s="248"/>
-      <c r="AE26" s="248"/>
-      <c r="AF26" s="248"/>
-      <c r="AG26" s="248"/>
-      <c r="AH26" s="248"/>
-      <c r="AI26" s="248"/>
-      <c r="AJ26" s="248"/>
-      <c r="AK26" s="248"/>
-      <c r="AL26" s="248"/>
-    </row>
-    <row r="27" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A27" s="247"/>
-      <c r="B27" s="247"/>
-      <c r="C27" s="247"/>
-      <c r="D27" s="247"/>
-      <c r="E27" s="247"/>
-      <c r="F27" s="247"/>
-      <c r="G27" s="247"/>
-      <c r="H27" s="247"/>
-      <c r="I27" s="247"/>
-      <c r="J27" s="247"/>
-      <c r="K27" s="247"/>
-      <c r="L27" s="247"/>
-      <c r="M27" s="247"/>
-      <c r="N27" s="247"/>
-      <c r="O27" s="248"/>
-      <c r="P27" s="248"/>
-      <c r="Q27" s="248"/>
-      <c r="R27" s="248"/>
-      <c r="S27" s="248"/>
-      <c r="T27" s="248"/>
-      <c r="U27" s="248"/>
-      <c r="V27" s="248"/>
-      <c r="W27" s="248"/>
-      <c r="X27" s="248"/>
-      <c r="Y27" s="248"/>
-      <c r="Z27" s="248"/>
-      <c r="AA27" s="248"/>
-      <c r="AB27" s="248"/>
-      <c r="AC27" s="248"/>
-      <c r="AD27" s="248"/>
-      <c r="AE27" s="248"/>
-      <c r="AF27" s="248"/>
-      <c r="AG27" s="248"/>
-      <c r="AH27" s="248"/>
-      <c r="AI27" s="248"/>
-      <c r="AJ27" s="248"/>
-      <c r="AK27" s="248"/>
-      <c r="AL27" s="248"/>
-    </row>
-    <row r="28" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A28" s="247" t="s">
-        <v>370</v>
-      </c>
-      <c r="B28" s="247"/>
-      <c r="C28" s="247"/>
-      <c r="D28" s="247"/>
-      <c r="E28" s="247"/>
-      <c r="F28" s="247"/>
-      <c r="G28" s="247"/>
-      <c r="H28" s="247" t="s">
+      <c r="I28" s="248"/>
+      <c r="J28" s="248"/>
+      <c r="K28" s="248"/>
+      <c r="L28" s="248"/>
+      <c r="M28" s="248"/>
+      <c r="N28" s="248"/>
+      <c r="O28" s="249"/>
+      <c r="P28" s="249"/>
+      <c r="Q28" s="249"/>
+      <c r="R28" s="249"/>
+      <c r="S28" s="249"/>
+      <c r="T28" s="249"/>
+      <c r="U28" s="249"/>
+      <c r="V28" s="249"/>
+      <c r="W28" s="249"/>
+      <c r="X28" s="249"/>
+      <c r="Y28" s="249"/>
+      <c r="Z28" s="249"/>
+      <c r="AA28" s="249"/>
+      <c r="AB28" s="249"/>
+      <c r="AC28" s="249"/>
+      <c r="AD28" s="249"/>
+      <c r="AE28" s="249"/>
+      <c r="AF28" s="249"/>
+      <c r="AG28" s="249"/>
+      <c r="AH28" s="249"/>
+      <c r="AI28" s="249"/>
+      <c r="AJ28" s="249"/>
+      <c r="AK28" s="249"/>
+      <c r="AL28" s="249"/>
+    </row>
+    <row r="29" spans="1:47" ht="16.95" customHeight="1">
+      <c r="A29" s="248"/>
+      <c r="B29" s="248"/>
+      <c r="C29" s="248"/>
+      <c r="D29" s="248"/>
+      <c r="E29" s="248"/>
+      <c r="F29" s="248"/>
+      <c r="G29" s="248"/>
+      <c r="H29" s="248"/>
+      <c r="I29" s="248"/>
+      <c r="J29" s="248"/>
+      <c r="K29" s="248"/>
+      <c r="L29" s="248"/>
+      <c r="M29" s="248"/>
+      <c r="N29" s="248"/>
+      <c r="O29" s="249"/>
+      <c r="P29" s="249"/>
+      <c r="Q29" s="249"/>
+      <c r="R29" s="249"/>
+      <c r="S29" s="249"/>
+      <c r="T29" s="249"/>
+      <c r="U29" s="249"/>
+      <c r="V29" s="249"/>
+      <c r="W29" s="249"/>
+      <c r="X29" s="249"/>
+      <c r="Y29" s="249"/>
+      <c r="Z29" s="249"/>
+      <c r="AA29" s="249"/>
+      <c r="AB29" s="249"/>
+      <c r="AC29" s="249"/>
+      <c r="AD29" s="249"/>
+      <c r="AE29" s="249"/>
+      <c r="AF29" s="249"/>
+      <c r="AG29" s="249"/>
+      <c r="AH29" s="249"/>
+      <c r="AI29" s="249"/>
+      <c r="AJ29" s="249"/>
+      <c r="AK29" s="249"/>
+      <c r="AL29" s="249"/>
+    </row>
+    <row r="30" spans="1:47" ht="16.95" customHeight="1">
+      <c r="A30" s="248"/>
+      <c r="B30" s="248"/>
+      <c r="C30" s="248"/>
+      <c r="D30" s="248"/>
+      <c r="E30" s="248"/>
+      <c r="F30" s="248"/>
+      <c r="G30" s="248"/>
+      <c r="H30" s="248" t="s">
         <v>378</v>
       </c>
-      <c r="I28" s="247"/>
-      <c r="J28" s="247"/>
-      <c r="K28" s="247"/>
-      <c r="L28" s="247"/>
-      <c r="M28" s="247"/>
-      <c r="N28" s="247"/>
-      <c r="O28" s="248"/>
-      <c r="P28" s="248"/>
-      <c r="Q28" s="248"/>
-      <c r="R28" s="248"/>
-      <c r="S28" s="248"/>
-      <c r="T28" s="248"/>
-      <c r="U28" s="248"/>
-      <c r="V28" s="248"/>
-      <c r="W28" s="248"/>
-      <c r="X28" s="248"/>
-      <c r="Y28" s="248"/>
-      <c r="Z28" s="248"/>
-      <c r="AA28" s="248"/>
-      <c r="AB28" s="248"/>
-      <c r="AC28" s="248"/>
-      <c r="AD28" s="248"/>
-      <c r="AE28" s="248"/>
-      <c r="AF28" s="248"/>
-      <c r="AG28" s="248"/>
-      <c r="AH28" s="248"/>
-      <c r="AI28" s="248"/>
-      <c r="AJ28" s="248"/>
-      <c r="AK28" s="248"/>
-      <c r="AL28" s="248"/>
-    </row>
-    <row r="29" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A29" s="247"/>
-      <c r="B29" s="247"/>
-      <c r="C29" s="247"/>
-      <c r="D29" s="247"/>
-      <c r="E29" s="247"/>
-      <c r="F29" s="247"/>
-      <c r="G29" s="247"/>
-      <c r="H29" s="247"/>
-      <c r="I29" s="247"/>
-      <c r="J29" s="247"/>
-      <c r="K29" s="247"/>
-      <c r="L29" s="247"/>
-      <c r="M29" s="247"/>
-      <c r="N29" s="247"/>
-      <c r="O29" s="248"/>
-      <c r="P29" s="248"/>
-      <c r="Q29" s="248"/>
-      <c r="R29" s="248"/>
-      <c r="S29" s="248"/>
-      <c r="T29" s="248"/>
-      <c r="U29" s="248"/>
-      <c r="V29" s="248"/>
-      <c r="W29" s="248"/>
-      <c r="X29" s="248"/>
-      <c r="Y29" s="248"/>
-      <c r="Z29" s="248"/>
-      <c r="AA29" s="248"/>
-      <c r="AB29" s="248"/>
-      <c r="AC29" s="248"/>
-      <c r="AD29" s="248"/>
-      <c r="AE29" s="248"/>
-      <c r="AF29" s="248"/>
-      <c r="AG29" s="248"/>
-      <c r="AH29" s="248"/>
-      <c r="AI29" s="248"/>
-      <c r="AJ29" s="248"/>
-      <c r="AK29" s="248"/>
-      <c r="AL29" s="248"/>
-    </row>
-    <row r="30" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A30" s="247"/>
-      <c r="B30" s="247"/>
-      <c r="C30" s="247"/>
-      <c r="D30" s="247"/>
-      <c r="E30" s="247"/>
-      <c r="F30" s="247"/>
-      <c r="G30" s="247"/>
-      <c r="H30" s="247" t="s">
+      <c r="I30" s="248"/>
+      <c r="J30" s="248"/>
+      <c r="K30" s="248"/>
+      <c r="L30" s="248"/>
+      <c r="M30" s="248"/>
+      <c r="N30" s="248"/>
+      <c r="O30" s="249"/>
+      <c r="P30" s="249"/>
+      <c r="Q30" s="249"/>
+      <c r="R30" s="249"/>
+      <c r="S30" s="249"/>
+      <c r="T30" s="249"/>
+      <c r="U30" s="249"/>
+      <c r="V30" s="249"/>
+      <c r="W30" s="249"/>
+      <c r="X30" s="249"/>
+      <c r="Y30" s="249"/>
+      <c r="Z30" s="249"/>
+      <c r="AA30" s="249"/>
+      <c r="AB30" s="249"/>
+      <c r="AC30" s="249"/>
+      <c r="AD30" s="249"/>
+      <c r="AE30" s="249"/>
+      <c r="AF30" s="249"/>
+      <c r="AG30" s="249"/>
+      <c r="AH30" s="249"/>
+      <c r="AI30" s="249"/>
+      <c r="AJ30" s="249"/>
+      <c r="AK30" s="249"/>
+      <c r="AL30" s="249"/>
+    </row>
+    <row r="31" spans="1:47" ht="16.95" customHeight="1">
+      <c r="A31" s="248"/>
+      <c r="B31" s="248"/>
+      <c r="C31" s="248"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="248"/>
+      <c r="M31" s="248"/>
+      <c r="N31" s="248"/>
+      <c r="O31" s="249"/>
+      <c r="P31" s="249"/>
+      <c r="Q31" s="249"/>
+      <c r="R31" s="249"/>
+      <c r="S31" s="249"/>
+      <c r="T31" s="249"/>
+      <c r="U31" s="249"/>
+      <c r="V31" s="249"/>
+      <c r="W31" s="249"/>
+      <c r="X31" s="249"/>
+      <c r="Y31" s="249"/>
+      <c r="Z31" s="249"/>
+      <c r="AA31" s="249"/>
+      <c r="AB31" s="249"/>
+      <c r="AC31" s="249"/>
+      <c r="AD31" s="249"/>
+      <c r="AE31" s="249"/>
+      <c r="AF31" s="249"/>
+      <c r="AG31" s="249"/>
+      <c r="AH31" s="249"/>
+      <c r="AI31" s="249"/>
+      <c r="AJ31" s="249"/>
+      <c r="AK31" s="249"/>
+      <c r="AL31" s="249"/>
+    </row>
+    <row r="32" spans="1:47" ht="16.95" customHeight="1">
+      <c r="A32" s="248" t="s">
+        <v>409</v>
+      </c>
+      <c r="B32" s="248"/>
+      <c r="C32" s="248"/>
+      <c r="D32" s="248"/>
+      <c r="E32" s="248"/>
+      <c r="F32" s="248"/>
+      <c r="G32" s="248"/>
+      <c r="H32" s="248"/>
+      <c r="I32" s="248"/>
+      <c r="J32" s="248"/>
+      <c r="K32" s="248"/>
+      <c r="L32" s="248"/>
+      <c r="M32" s="248"/>
+      <c r="N32" s="248"/>
+      <c r="O32" s="249"/>
+      <c r="P32" s="249"/>
+      <c r="Q32" s="249"/>
+      <c r="R32" s="249"/>
+      <c r="S32" s="249"/>
+      <c r="T32" s="249"/>
+      <c r="U32" s="249"/>
+      <c r="V32" s="249"/>
+      <c r="W32" s="249"/>
+      <c r="X32" s="249"/>
+      <c r="Y32" s="249"/>
+      <c r="Z32" s="249"/>
+      <c r="AA32" s="249"/>
+      <c r="AB32" s="249"/>
+      <c r="AC32" s="249"/>
+      <c r="AD32" s="249"/>
+      <c r="AE32" s="249"/>
+      <c r="AF32" s="249"/>
+      <c r="AG32" s="249"/>
+      <c r="AH32" s="249"/>
+      <c r="AI32" s="249"/>
+      <c r="AJ32" s="249"/>
+      <c r="AK32" s="249"/>
+      <c r="AL32" s="249"/>
+    </row>
+    <row r="33" spans="1:39" ht="16.95" customHeight="1">
+      <c r="A33" s="248"/>
+      <c r="B33" s="248"/>
+      <c r="C33" s="248"/>
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="248"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="248"/>
+      <c r="K33" s="248"/>
+      <c r="L33" s="248"/>
+      <c r="M33" s="248"/>
+      <c r="N33" s="248"/>
+      <c r="O33" s="249"/>
+      <c r="P33" s="249"/>
+      <c r="Q33" s="249"/>
+      <c r="R33" s="249"/>
+      <c r="S33" s="249"/>
+      <c r="T33" s="249"/>
+      <c r="U33" s="249"/>
+      <c r="V33" s="249"/>
+      <c r="W33" s="249"/>
+      <c r="X33" s="249"/>
+      <c r="Y33" s="249"/>
+      <c r="Z33" s="249"/>
+      <c r="AA33" s="249"/>
+      <c r="AB33" s="249"/>
+      <c r="AC33" s="249"/>
+      <c r="AD33" s="249"/>
+      <c r="AE33" s="249"/>
+      <c r="AF33" s="249"/>
+      <c r="AG33" s="249"/>
+      <c r="AH33" s="249"/>
+      <c r="AI33" s="249"/>
+      <c r="AJ33" s="249"/>
+      <c r="AK33" s="249"/>
+      <c r="AL33" s="249"/>
+    </row>
+    <row r="34" spans="1:39" ht="16.95" customHeight="1">
+      <c r="A34" s="248" t="s">
         <v>379</v>
       </c>
-      <c r="I30" s="247"/>
-      <c r="J30" s="247"/>
-      <c r="K30" s="247"/>
-      <c r="L30" s="247"/>
-      <c r="M30" s="247"/>
-      <c r="N30" s="247"/>
-      <c r="O30" s="248"/>
-      <c r="P30" s="248"/>
-      <c r="Q30" s="248"/>
-      <c r="R30" s="248"/>
-      <c r="S30" s="248"/>
-      <c r="T30" s="248"/>
-      <c r="U30" s="248"/>
-      <c r="V30" s="248"/>
-      <c r="W30" s="248"/>
-      <c r="X30" s="248"/>
-      <c r="Y30" s="248"/>
-      <c r="Z30" s="248"/>
-      <c r="AA30" s="248"/>
-      <c r="AB30" s="248"/>
-      <c r="AC30" s="248"/>
-      <c r="AD30" s="248"/>
-      <c r="AE30" s="248"/>
-      <c r="AF30" s="248"/>
-      <c r="AG30" s="248"/>
-      <c r="AH30" s="248"/>
-      <c r="AI30" s="248"/>
-      <c r="AJ30" s="248"/>
-      <c r="AK30" s="248"/>
-      <c r="AL30" s="248"/>
-    </row>
-    <row r="31" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A31" s="247"/>
-      <c r="B31" s="247"/>
-      <c r="C31" s="247"/>
-      <c r="D31" s="247"/>
-      <c r="E31" s="247"/>
-      <c r="F31" s="247"/>
-      <c r="G31" s="247"/>
-      <c r="H31" s="247"/>
-      <c r="I31" s="247"/>
-      <c r="J31" s="247"/>
-      <c r="K31" s="247"/>
-      <c r="L31" s="247"/>
-      <c r="M31" s="247"/>
-      <c r="N31" s="247"/>
-      <c r="O31" s="248"/>
-      <c r="P31" s="248"/>
-      <c r="Q31" s="248"/>
-      <c r="R31" s="248"/>
-      <c r="S31" s="248"/>
-      <c r="T31" s="248"/>
-      <c r="U31" s="248"/>
-      <c r="V31" s="248"/>
-      <c r="W31" s="248"/>
-      <c r="X31" s="248"/>
-      <c r="Y31" s="248"/>
-      <c r="Z31" s="248"/>
-      <c r="AA31" s="248"/>
-      <c r="AB31" s="248"/>
-      <c r="AC31" s="248"/>
-      <c r="AD31" s="248"/>
-      <c r="AE31" s="248"/>
-      <c r="AF31" s="248"/>
-      <c r="AG31" s="248"/>
-      <c r="AH31" s="248"/>
-      <c r="AI31" s="248"/>
-      <c r="AJ31" s="248"/>
-      <c r="AK31" s="248"/>
-      <c r="AL31" s="248"/>
-    </row>
-    <row r="32" spans="1:47" ht="16.95" customHeight="1">
-      <c r="A32" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B32" s="247"/>
-      <c r="C32" s="247"/>
-      <c r="D32" s="247"/>
-      <c r="E32" s="247"/>
-      <c r="F32" s="247"/>
-      <c r="G32" s="247"/>
-      <c r="H32" s="247"/>
-      <c r="I32" s="247"/>
-      <c r="J32" s="247"/>
-      <c r="K32" s="247"/>
-      <c r="L32" s="247"/>
-      <c r="M32" s="247"/>
-      <c r="N32" s="247"/>
-      <c r="O32" s="248"/>
-      <c r="P32" s="248"/>
-      <c r="Q32" s="248"/>
-      <c r="R32" s="248"/>
-      <c r="S32" s="248"/>
-      <c r="T32" s="248"/>
-      <c r="U32" s="248"/>
-      <c r="V32" s="248"/>
-      <c r="W32" s="248"/>
-      <c r="X32" s="248"/>
-      <c r="Y32" s="248"/>
-      <c r="Z32" s="248"/>
-      <c r="AA32" s="248"/>
-      <c r="AB32" s="248"/>
-      <c r="AC32" s="248"/>
-      <c r="AD32" s="248"/>
-      <c r="AE32" s="248"/>
-      <c r="AF32" s="248"/>
-      <c r="AG32" s="248"/>
-      <c r="AH32" s="248"/>
-      <c r="AI32" s="248"/>
-      <c r="AJ32" s="248"/>
-      <c r="AK32" s="248"/>
-      <c r="AL32" s="248"/>
-    </row>
-    <row r="33" spans="1:39" ht="16.95" customHeight="1">
-      <c r="A33" s="247"/>
-      <c r="B33" s="247"/>
-      <c r="C33" s="247"/>
-      <c r="D33" s="247"/>
-      <c r="E33" s="247"/>
-      <c r="F33" s="247"/>
-      <c r="G33" s="247"/>
-      <c r="H33" s="247"/>
-      <c r="I33" s="247"/>
-      <c r="J33" s="247"/>
-      <c r="K33" s="247"/>
-      <c r="L33" s="247"/>
-      <c r="M33" s="247"/>
-      <c r="N33" s="247"/>
-      <c r="O33" s="248"/>
-      <c r="P33" s="248"/>
-      <c r="Q33" s="248"/>
-      <c r="R33" s="248"/>
-      <c r="S33" s="248"/>
-      <c r="T33" s="248"/>
-      <c r="U33" s="248"/>
-      <c r="V33" s="248"/>
-      <c r="W33" s="248"/>
-      <c r="X33" s="248"/>
-      <c r="Y33" s="248"/>
-      <c r="Z33" s="248"/>
-      <c r="AA33" s="248"/>
-      <c r="AB33" s="248"/>
-      <c r="AC33" s="248"/>
-      <c r="AD33" s="248"/>
-      <c r="AE33" s="248"/>
-      <c r="AF33" s="248"/>
-      <c r="AG33" s="248"/>
-      <c r="AH33" s="248"/>
-      <c r="AI33" s="248"/>
-      <c r="AJ33" s="248"/>
-      <c r="AK33" s="248"/>
-      <c r="AL33" s="248"/>
-    </row>
-    <row r="34" spans="1:39" ht="16.95" customHeight="1">
-      <c r="A34" s="247" t="s">
-        <v>380</v>
-      </c>
-      <c r="B34" s="247"/>
-      <c r="C34" s="247"/>
-      <c r="D34" s="247"/>
-      <c r="E34" s="247"/>
-      <c r="F34" s="247"/>
-      <c r="G34" s="247"/>
-      <c r="H34" s="247"/>
-      <c r="I34" s="247"/>
-      <c r="J34" s="247"/>
-      <c r="K34" s="247"/>
-      <c r="L34" s="247"/>
-      <c r="M34" s="247"/>
-      <c r="N34" s="247"/>
-      <c r="O34" s="248"/>
-      <c r="P34" s="248"/>
-      <c r="Q34" s="248"/>
-      <c r="R34" s="248"/>
-      <c r="S34" s="248"/>
-      <c r="T34" s="248"/>
-      <c r="U34" s="248"/>
-      <c r="V34" s="248"/>
-      <c r="W34" s="248"/>
-      <c r="X34" s="248"/>
-      <c r="Y34" s="248"/>
-      <c r="Z34" s="248"/>
-      <c r="AA34" s="248"/>
-      <c r="AB34" s="248"/>
-      <c r="AC34" s="248"/>
-      <c r="AD34" s="248"/>
-      <c r="AE34" s="248"/>
-      <c r="AF34" s="248"/>
-      <c r="AG34" s="248"/>
-      <c r="AH34" s="248"/>
-      <c r="AI34" s="248"/>
-      <c r="AJ34" s="248"/>
-      <c r="AK34" s="248"/>
-      <c r="AL34" s="248"/>
+      <c r="B34" s="248"/>
+      <c r="C34" s="248"/>
+      <c r="D34" s="248"/>
+      <c r="E34" s="248"/>
+      <c r="F34" s="248"/>
+      <c r="G34" s="248"/>
+      <c r="H34" s="248"/>
+      <c r="I34" s="248"/>
+      <c r="J34" s="248"/>
+      <c r="K34" s="248"/>
+      <c r="L34" s="248"/>
+      <c r="M34" s="248"/>
+      <c r="N34" s="248"/>
+      <c r="O34" s="249"/>
+      <c r="P34" s="249"/>
+      <c r="Q34" s="249"/>
+      <c r="R34" s="249"/>
+      <c r="S34" s="249"/>
+      <c r="T34" s="249"/>
+      <c r="U34" s="249"/>
+      <c r="V34" s="249"/>
+      <c r="W34" s="249"/>
+      <c r="X34" s="249"/>
+      <c r="Y34" s="249"/>
+      <c r="Z34" s="249"/>
+      <c r="AA34" s="249"/>
+      <c r="AB34" s="249"/>
+      <c r="AC34" s="249"/>
+      <c r="AD34" s="249"/>
+      <c r="AE34" s="249"/>
+      <c r="AF34" s="249"/>
+      <c r="AG34" s="249"/>
+      <c r="AH34" s="249"/>
+      <c r="AI34" s="249"/>
+      <c r="AJ34" s="249"/>
+      <c r="AK34" s="249"/>
+      <c r="AL34" s="249"/>
     </row>
     <row r="35" spans="1:39" ht="16.95" customHeight="1">
-      <c r="A35" s="247"/>
-      <c r="B35" s="247"/>
-      <c r="C35" s="247"/>
-      <c r="D35" s="247"/>
-      <c r="E35" s="247"/>
-      <c r="F35" s="247"/>
-      <c r="G35" s="247"/>
-      <c r="H35" s="247"/>
-      <c r="I35" s="247"/>
-      <c r="J35" s="247"/>
-      <c r="K35" s="247"/>
-      <c r="L35" s="247"/>
-      <c r="M35" s="247"/>
-      <c r="N35" s="247"/>
-      <c r="O35" s="248"/>
-      <c r="P35" s="248"/>
-      <c r="Q35" s="248"/>
-      <c r="R35" s="248"/>
-      <c r="S35" s="248"/>
-      <c r="T35" s="248"/>
-      <c r="U35" s="248"/>
-      <c r="V35" s="248"/>
-      <c r="W35" s="248"/>
-      <c r="X35" s="248"/>
-      <c r="Y35" s="248"/>
-      <c r="Z35" s="248"/>
-      <c r="AA35" s="248"/>
-      <c r="AB35" s="248"/>
-      <c r="AC35" s="248"/>
-      <c r="AD35" s="248"/>
-      <c r="AE35" s="248"/>
-      <c r="AF35" s="248"/>
-      <c r="AG35" s="248"/>
-      <c r="AH35" s="248"/>
-      <c r="AI35" s="248"/>
-      <c r="AJ35" s="248"/>
-      <c r="AK35" s="248"/>
-      <c r="AL35" s="248"/>
+      <c r="A35" s="248"/>
+      <c r="B35" s="248"/>
+      <c r="C35" s="248"/>
+      <c r="D35" s="248"/>
+      <c r="E35" s="248"/>
+      <c r="F35" s="248"/>
+      <c r="G35" s="248"/>
+      <c r="H35" s="248"/>
+      <c r="I35" s="248"/>
+      <c r="J35" s="248"/>
+      <c r="K35" s="248"/>
+      <c r="L35" s="248"/>
+      <c r="M35" s="248"/>
+      <c r="N35" s="248"/>
+      <c r="O35" s="249"/>
+      <c r="P35" s="249"/>
+      <c r="Q35" s="249"/>
+      <c r="R35" s="249"/>
+      <c r="S35" s="249"/>
+      <c r="T35" s="249"/>
+      <c r="U35" s="249"/>
+      <c r="V35" s="249"/>
+      <c r="W35" s="249"/>
+      <c r="X35" s="249"/>
+      <c r="Y35" s="249"/>
+      <c r="Z35" s="249"/>
+      <c r="AA35" s="249"/>
+      <c r="AB35" s="249"/>
+      <c r="AC35" s="249"/>
+      <c r="AD35" s="249"/>
+      <c r="AE35" s="249"/>
+      <c r="AF35" s="249"/>
+      <c r="AG35" s="249"/>
+      <c r="AH35" s="249"/>
+      <c r="AI35" s="249"/>
+      <c r="AJ35" s="249"/>
+      <c r="AK35" s="249"/>
+      <c r="AL35" s="249"/>
     </row>
     <row r="36" spans="1:39" ht="18" customHeight="1">
       <c r="A36" s="6" t="s">
@@ -18380,12 +18817,12 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="26"/>
-      <c r="F5" s="274"/>
-      <c r="G5" s="274"/>
-      <c r="H5" s="274"/>
-      <c r="I5" s="274"/>
-      <c r="J5" s="274"/>
-      <c r="K5" s="274"/>
+      <c r="F5" s="270"/>
+      <c r="G5" s="270"/>
+      <c r="H5" s="270"/>
+      <c r="I5" s="270"/>
+      <c r="J5" s="270"/>
+      <c r="K5" s="270"/>
       <c r="L5" s="6" t="s">
         <v>106</v>
       </c>
@@ -18423,13 +18860,13 @@
       <c r="B6" s="6"/>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
-      <c r="E6" s="274"/>
-      <c r="F6" s="274"/>
-      <c r="G6" s="274"/>
-      <c r="H6" s="274"/>
-      <c r="I6" s="274"/>
-      <c r="J6" s="274"/>
-      <c r="K6" s="274"/>
+      <c r="E6" s="270"/>
+      <c r="F6" s="270"/>
+      <c r="G6" s="270"/>
+      <c r="H6" s="270"/>
+      <c r="I6" s="270"/>
+      <c r="J6" s="270"/>
+      <c r="K6" s="270"/>
       <c r="L6" s="6" t="s">
         <v>108</v>
       </c>
@@ -18471,13 +18908,13 @@
       <c r="F7" s="28"/>
       <c r="G7" s="28"/>
       <c r="H7" s="28"/>
-      <c r="I7" s="275"/>
-      <c r="J7" s="275"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="275"/>
-      <c r="M7" s="275"/>
-      <c r="N7" s="275"/>
-      <c r="O7" s="275"/>
+      <c r="I7" s="271"/>
+      <c r="J7" s="271"/>
+      <c r="K7" s="271"/>
+      <c r="L7" s="271"/>
+      <c r="M7" s="271"/>
+      <c r="N7" s="271"/>
+      <c r="O7" s="271"/>
       <c r="P7" s="28"/>
       <c r="Q7" s="28"/>
       <c r="R7" s="28"/>
@@ -18593,544 +19030,544 @@
       <c r="D10" s="222"/>
       <c r="E10" s="222"/>
       <c r="F10" s="222"/>
-      <c r="G10" s="272" t="s">
+      <c r="G10" s="274" t="s">
         <v>111</v>
       </c>
-      <c r="H10" s="273"/>
+      <c r="H10" s="275"/>
       <c r="I10" s="223"/>
-      <c r="J10" s="271"/>
-      <c r="K10" s="271"/>
-      <c r="L10" s="271"/>
-      <c r="M10" s="271"/>
-      <c r="N10" s="271"/>
-      <c r="O10" s="271"/>
-      <c r="P10" s="271"/>
-      <c r="Q10" s="271"/>
-      <c r="R10" s="271"/>
-      <c r="S10" s="271"/>
-      <c r="T10" s="271"/>
-      <c r="U10" s="271"/>
-      <c r="V10" s="271"/>
-      <c r="W10" s="271"/>
-      <c r="X10" s="271"/>
-      <c r="Y10" s="271"/>
-      <c r="Z10" s="271"/>
-      <c r="AA10" s="271"/>
-      <c r="AB10" s="271"/>
-      <c r="AC10" s="271"/>
-      <c r="AD10" s="271"/>
-      <c r="AE10" s="271"/>
-      <c r="AF10" s="271"/>
-      <c r="AG10" s="271"/>
-      <c r="AH10" s="271"/>
-      <c r="AI10" s="271"/>
-      <c r="AJ10" s="271"/>
-      <c r="AK10" s="271"/>
-      <c r="AL10" s="271"/>
+      <c r="J10" s="272"/>
+      <c r="K10" s="272"/>
+      <c r="L10" s="272"/>
+      <c r="M10" s="272"/>
+      <c r="N10" s="272"/>
+      <c r="O10" s="272"/>
+      <c r="P10" s="272"/>
+      <c r="Q10" s="272"/>
+      <c r="R10" s="272"/>
+      <c r="S10" s="272"/>
+      <c r="T10" s="272"/>
+      <c r="U10" s="272"/>
+      <c r="V10" s="272"/>
+      <c r="W10" s="272"/>
+      <c r="X10" s="272"/>
+      <c r="Y10" s="272"/>
+      <c r="Z10" s="272"/>
+      <c r="AA10" s="272"/>
+      <c r="AB10" s="272"/>
+      <c r="AC10" s="272"/>
+      <c r="AD10" s="272"/>
+      <c r="AE10" s="272"/>
+      <c r="AF10" s="272"/>
+      <c r="AG10" s="272"/>
+      <c r="AH10" s="272"/>
+      <c r="AI10" s="272"/>
+      <c r="AJ10" s="272"/>
+      <c r="AK10" s="272"/>
+      <c r="AL10" s="272"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1">
-      <c r="A11" s="248" t="s">
+      <c r="A11" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="248"/>
-      <c r="C11" s="270"/>
-      <c r="D11" s="270"/>
-      <c r="E11" s="270"/>
-      <c r="F11" s="270"/>
-      <c r="G11" s="270"/>
-      <c r="H11" s="270"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
-      <c r="M11" s="248"/>
-      <c r="N11" s="248"/>
-      <c r="O11" s="248"/>
-      <c r="P11" s="248"/>
-      <c r="Q11" s="248"/>
-      <c r="R11" s="248"/>
-      <c r="S11" s="248"/>
-      <c r="T11" s="248"/>
-      <c r="U11" s="248"/>
-      <c r="V11" s="248"/>
-      <c r="W11" s="248"/>
-      <c r="X11" s="248"/>
-      <c r="Y11" s="248"/>
-      <c r="Z11" s="248"/>
-      <c r="AA11" s="248"/>
-      <c r="AB11" s="248"/>
-      <c r="AC11" s="248"/>
-      <c r="AD11" s="248"/>
-      <c r="AE11" s="248"/>
-      <c r="AF11" s="248"/>
-      <c r="AG11" s="248"/>
-      <c r="AH11" s="248"/>
-      <c r="AI11" s="248"/>
-      <c r="AJ11" s="248"/>
-      <c r="AK11" s="248"/>
-      <c r="AL11" s="248"/>
+      <c r="B11" s="249"/>
+      <c r="C11" s="273"/>
+      <c r="D11" s="273"/>
+      <c r="E11" s="273"/>
+      <c r="F11" s="273"/>
+      <c r="G11" s="273"/>
+      <c r="H11" s="273"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
+      <c r="M11" s="249"/>
+      <c r="N11" s="249"/>
+      <c r="O11" s="249"/>
+      <c r="P11" s="249"/>
+      <c r="Q11" s="249"/>
+      <c r="R11" s="249"/>
+      <c r="S11" s="249"/>
+      <c r="T11" s="249"/>
+      <c r="U11" s="249"/>
+      <c r="V11" s="249"/>
+      <c r="W11" s="249"/>
+      <c r="X11" s="249"/>
+      <c r="Y11" s="249"/>
+      <c r="Z11" s="249"/>
+      <c r="AA11" s="249"/>
+      <c r="AB11" s="249"/>
+      <c r="AC11" s="249"/>
+      <c r="AD11" s="249"/>
+      <c r="AE11" s="249"/>
+      <c r="AF11" s="249"/>
+      <c r="AG11" s="249"/>
+      <c r="AH11" s="249"/>
+      <c r="AI11" s="249"/>
+      <c r="AJ11" s="249"/>
+      <c r="AK11" s="249"/>
+      <c r="AL11" s="249"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
-      <c r="A12" s="248" t="s">
+      <c r="A12" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="248"/>
-      <c r="C12" s="248"/>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="248"/>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="248"/>
-      <c r="K12" s="248"/>
-      <c r="L12" s="248"/>
-      <c r="M12" s="248"/>
-      <c r="N12" s="248"/>
-      <c r="O12" s="248"/>
-      <c r="P12" s="248"/>
-      <c r="Q12" s="248"/>
-      <c r="R12" s="248"/>
-      <c r="S12" s="248"/>
-      <c r="T12" s="248"/>
-      <c r="U12" s="248"/>
-      <c r="V12" s="248"/>
-      <c r="W12" s="248"/>
-      <c r="X12" s="248"/>
-      <c r="Y12" s="248"/>
-      <c r="Z12" s="248"/>
-      <c r="AA12" s="248"/>
-      <c r="AB12" s="248"/>
-      <c r="AC12" s="248"/>
-      <c r="AD12" s="248"/>
-      <c r="AE12" s="248"/>
-      <c r="AF12" s="248"/>
-      <c r="AG12" s="248"/>
-      <c r="AH12" s="248"/>
-      <c r="AI12" s="248"/>
-      <c r="AJ12" s="248"/>
-      <c r="AK12" s="248"/>
-      <c r="AL12" s="248"/>
+      <c r="B12" s="249"/>
+      <c r="C12" s="249"/>
+      <c r="D12" s="249"/>
+      <c r="E12" s="249"/>
+      <c r="F12" s="249"/>
+      <c r="G12" s="249"/>
+      <c r="H12" s="249"/>
+      <c r="I12" s="249"/>
+      <c r="J12" s="249"/>
+      <c r="K12" s="249"/>
+      <c r="L12" s="249"/>
+      <c r="M12" s="249"/>
+      <c r="N12" s="249"/>
+      <c r="O12" s="249"/>
+      <c r="P12" s="249"/>
+      <c r="Q12" s="249"/>
+      <c r="R12" s="249"/>
+      <c r="S12" s="249"/>
+      <c r="T12" s="249"/>
+      <c r="U12" s="249"/>
+      <c r="V12" s="249"/>
+      <c r="W12" s="249"/>
+      <c r="X12" s="249"/>
+      <c r="Y12" s="249"/>
+      <c r="Z12" s="249"/>
+      <c r="AA12" s="249"/>
+      <c r="AB12" s="249"/>
+      <c r="AC12" s="249"/>
+      <c r="AD12" s="249"/>
+      <c r="AE12" s="249"/>
+      <c r="AF12" s="249"/>
+      <c r="AG12" s="249"/>
+      <c r="AH12" s="249"/>
+      <c r="AI12" s="249"/>
+      <c r="AJ12" s="249"/>
+      <c r="AK12" s="249"/>
+      <c r="AL12" s="249"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
-      <c r="A13" s="248" t="s">
+      <c r="A13" s="249" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="248"/>
-      <c r="C13" s="248"/>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="248"/>
-      <c r="J13" s="248"/>
-      <c r="K13" s="248"/>
-      <c r="L13" s="248"/>
-      <c r="M13" s="248"/>
-      <c r="N13" s="248"/>
-      <c r="O13" s="248"/>
-      <c r="P13" s="248"/>
-      <c r="Q13" s="248"/>
-      <c r="R13" s="248"/>
-      <c r="S13" s="248"/>
-      <c r="T13" s="248"/>
-      <c r="U13" s="248"/>
-      <c r="V13" s="248"/>
-      <c r="W13" s="248"/>
-      <c r="X13" s="248"/>
-      <c r="Y13" s="248"/>
-      <c r="Z13" s="248"/>
-      <c r="AA13" s="248"/>
-      <c r="AB13" s="248"/>
-      <c r="AC13" s="248"/>
-      <c r="AD13" s="248"/>
-      <c r="AE13" s="248"/>
-      <c r="AF13" s="248"/>
-      <c r="AG13" s="248"/>
-      <c r="AH13" s="248"/>
-      <c r="AI13" s="248"/>
-      <c r="AJ13" s="248"/>
-      <c r="AK13" s="248"/>
-      <c r="AL13" s="248"/>
+      <c r="B13" s="249"/>
+      <c r="C13" s="249"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="249"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="249"/>
+      <c r="I13" s="249"/>
+      <c r="J13" s="249"/>
+      <c r="K13" s="249"/>
+      <c r="L13" s="249"/>
+      <c r="M13" s="249"/>
+      <c r="N13" s="249"/>
+      <c r="O13" s="249"/>
+      <c r="P13" s="249"/>
+      <c r="Q13" s="249"/>
+      <c r="R13" s="249"/>
+      <c r="S13" s="249"/>
+      <c r="T13" s="249"/>
+      <c r="U13" s="249"/>
+      <c r="V13" s="249"/>
+      <c r="W13" s="249"/>
+      <c r="X13" s="249"/>
+      <c r="Y13" s="249"/>
+      <c r="Z13" s="249"/>
+      <c r="AA13" s="249"/>
+      <c r="AB13" s="249"/>
+      <c r="AC13" s="249"/>
+      <c r="AD13" s="249"/>
+      <c r="AE13" s="249"/>
+      <c r="AF13" s="249"/>
+      <c r="AG13" s="249"/>
+      <c r="AH13" s="249"/>
+      <c r="AI13" s="249"/>
+      <c r="AJ13" s="249"/>
+      <c r="AK13" s="249"/>
+      <c r="AL13" s="249"/>
     </row>
     <row r="14" spans="1:38" ht="18" customHeight="1">
-      <c r="A14" s="248" t="s">
+      <c r="A14" s="249" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="248"/>
-      <c r="C14" s="248"/>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="248"/>
-      <c r="G14" s="248"/>
-      <c r="H14" s="248"/>
-      <c r="I14" s="248"/>
-      <c r="J14" s="248"/>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
-      <c r="M14" s="248"/>
-      <c r="N14" s="248"/>
-      <c r="O14" s="248"/>
-      <c r="P14" s="248"/>
-      <c r="Q14" s="248"/>
-      <c r="R14" s="248"/>
-      <c r="S14" s="248"/>
-      <c r="T14" s="248"/>
-      <c r="U14" s="248"/>
-      <c r="V14" s="248"/>
-      <c r="W14" s="248"/>
-      <c r="X14" s="248"/>
-      <c r="Y14" s="248"/>
-      <c r="Z14" s="248"/>
-      <c r="AA14" s="248"/>
-      <c r="AB14" s="248"/>
-      <c r="AC14" s="248"/>
-      <c r="AD14" s="248"/>
-      <c r="AE14" s="248"/>
-      <c r="AF14" s="248"/>
-      <c r="AG14" s="248"/>
-      <c r="AH14" s="248"/>
-      <c r="AI14" s="248"/>
-      <c r="AJ14" s="248"/>
-      <c r="AK14" s="248"/>
-      <c r="AL14" s="248"/>
+      <c r="B14" s="249"/>
+      <c r="C14" s="249"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="249"/>
+      <c r="K14" s="249"/>
+      <c r="L14" s="249"/>
+      <c r="M14" s="249"/>
+      <c r="N14" s="249"/>
+      <c r="O14" s="249"/>
+      <c r="P14" s="249"/>
+      <c r="Q14" s="249"/>
+      <c r="R14" s="249"/>
+      <c r="S14" s="249"/>
+      <c r="T14" s="249"/>
+      <c r="U14" s="249"/>
+      <c r="V14" s="249"/>
+      <c r="W14" s="249"/>
+      <c r="X14" s="249"/>
+      <c r="Y14" s="249"/>
+      <c r="Z14" s="249"/>
+      <c r="AA14" s="249"/>
+      <c r="AB14" s="249"/>
+      <c r="AC14" s="249"/>
+      <c r="AD14" s="249"/>
+      <c r="AE14" s="249"/>
+      <c r="AF14" s="249"/>
+      <c r="AG14" s="249"/>
+      <c r="AH14" s="249"/>
+      <c r="AI14" s="249"/>
+      <c r="AJ14" s="249"/>
+      <c r="AK14" s="249"/>
+      <c r="AL14" s="249"/>
     </row>
     <row r="15" spans="1:38" ht="18" customHeight="1">
-      <c r="A15" s="248" t="s">
+      <c r="A15" s="249" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="248"/>
-      <c r="C15" s="248"/>
-      <c r="D15" s="248"/>
-      <c r="E15" s="248"/>
-      <c r="F15" s="248"/>
-      <c r="G15" s="248"/>
-      <c r="H15" s="248"/>
-      <c r="I15" s="248"/>
-      <c r="J15" s="248"/>
-      <c r="K15" s="248"/>
-      <c r="L15" s="248"/>
-      <c r="M15" s="248"/>
-      <c r="N15" s="248"/>
-      <c r="O15" s="248"/>
-      <c r="P15" s="248"/>
-      <c r="Q15" s="248"/>
-      <c r="R15" s="248"/>
-      <c r="S15" s="248"/>
-      <c r="T15" s="248"/>
-      <c r="U15" s="248"/>
-      <c r="V15" s="248"/>
-      <c r="W15" s="248"/>
-      <c r="X15" s="248"/>
-      <c r="Y15" s="248"/>
-      <c r="Z15" s="248"/>
-      <c r="AA15" s="248"/>
-      <c r="AB15" s="248"/>
-      <c r="AC15" s="248"/>
-      <c r="AD15" s="248"/>
-      <c r="AE15" s="248"/>
-      <c r="AF15" s="248"/>
-      <c r="AG15" s="248"/>
-      <c r="AH15" s="248"/>
-      <c r="AI15" s="248"/>
-      <c r="AJ15" s="248"/>
-      <c r="AK15" s="248"/>
-      <c r="AL15" s="248"/>
+      <c r="B15" s="249"/>
+      <c r="C15" s="249"/>
+      <c r="D15" s="249"/>
+      <c r="E15" s="249"/>
+      <c r="F15" s="249"/>
+      <c r="G15" s="249"/>
+      <c r="H15" s="249"/>
+      <c r="I15" s="249"/>
+      <c r="J15" s="249"/>
+      <c r="K15" s="249"/>
+      <c r="L15" s="249"/>
+      <c r="M15" s="249"/>
+      <c r="N15" s="249"/>
+      <c r="O15" s="249"/>
+      <c r="P15" s="249"/>
+      <c r="Q15" s="249"/>
+      <c r="R15" s="249"/>
+      <c r="S15" s="249"/>
+      <c r="T15" s="249"/>
+      <c r="U15" s="249"/>
+      <c r="V15" s="249"/>
+      <c r="W15" s="249"/>
+      <c r="X15" s="249"/>
+      <c r="Y15" s="249"/>
+      <c r="Z15" s="249"/>
+      <c r="AA15" s="249"/>
+      <c r="AB15" s="249"/>
+      <c r="AC15" s="249"/>
+      <c r="AD15" s="249"/>
+      <c r="AE15" s="249"/>
+      <c r="AF15" s="249"/>
+      <c r="AG15" s="249"/>
+      <c r="AH15" s="249"/>
+      <c r="AI15" s="249"/>
+      <c r="AJ15" s="249"/>
+      <c r="AK15" s="249"/>
+      <c r="AL15" s="249"/>
     </row>
     <row r="16" spans="1:38" ht="18" customHeight="1">
-      <c r="A16" s="248" t="s">
+      <c r="A16" s="249" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="248"/>
-      <c r="C16" s="248"/>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
-      <c r="F16" s="248"/>
-      <c r="G16" s="248"/>
-      <c r="H16" s="248"/>
-      <c r="I16" s="248"/>
-      <c r="J16" s="248"/>
-      <c r="K16" s="248"/>
-      <c r="L16" s="248"/>
-      <c r="M16" s="248"/>
-      <c r="N16" s="248"/>
-      <c r="O16" s="248"/>
-      <c r="P16" s="248"/>
-      <c r="Q16" s="248"/>
-      <c r="R16" s="248"/>
-      <c r="S16" s="248"/>
-      <c r="T16" s="248"/>
-      <c r="U16" s="248"/>
-      <c r="V16" s="248"/>
-      <c r="W16" s="248"/>
-      <c r="X16" s="248"/>
-      <c r="Y16" s="248"/>
-      <c r="Z16" s="248"/>
-      <c r="AA16" s="248"/>
-      <c r="AB16" s="248"/>
-      <c r="AC16" s="248"/>
-      <c r="AD16" s="248"/>
-      <c r="AE16" s="248"/>
-      <c r="AF16" s="248"/>
-      <c r="AG16" s="248"/>
-      <c r="AH16" s="248"/>
-      <c r="AI16" s="248"/>
-      <c r="AJ16" s="248"/>
-      <c r="AK16" s="248"/>
-      <c r="AL16" s="248"/>
+      <c r="B16" s="249"/>
+      <c r="C16" s="249"/>
+      <c r="D16" s="249"/>
+      <c r="E16" s="249"/>
+      <c r="F16" s="249"/>
+      <c r="G16" s="249"/>
+      <c r="H16" s="249"/>
+      <c r="I16" s="249"/>
+      <c r="J16" s="249"/>
+      <c r="K16" s="249"/>
+      <c r="L16" s="249"/>
+      <c r="M16" s="249"/>
+      <c r="N16" s="249"/>
+      <c r="O16" s="249"/>
+      <c r="P16" s="249"/>
+      <c r="Q16" s="249"/>
+      <c r="R16" s="249"/>
+      <c r="S16" s="249"/>
+      <c r="T16" s="249"/>
+      <c r="U16" s="249"/>
+      <c r="V16" s="249"/>
+      <c r="W16" s="249"/>
+      <c r="X16" s="249"/>
+      <c r="Y16" s="249"/>
+      <c r="Z16" s="249"/>
+      <c r="AA16" s="249"/>
+      <c r="AB16" s="249"/>
+      <c r="AC16" s="249"/>
+      <c r="AD16" s="249"/>
+      <c r="AE16" s="249"/>
+      <c r="AF16" s="249"/>
+      <c r="AG16" s="249"/>
+      <c r="AH16" s="249"/>
+      <c r="AI16" s="249"/>
+      <c r="AJ16" s="249"/>
+      <c r="AK16" s="249"/>
+      <c r="AL16" s="249"/>
     </row>
     <row r="17" spans="1:38" ht="18" customHeight="1">
-      <c r="A17" s="248" t="s">
+      <c r="A17" s="249" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="248"/>
-      <c r="C17" s="248"/>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
-      <c r="M17" s="248"/>
-      <c r="N17" s="248"/>
-      <c r="O17" s="248"/>
-      <c r="P17" s="248"/>
-      <c r="Q17" s="248"/>
-      <c r="R17" s="248"/>
-      <c r="S17" s="248"/>
-      <c r="T17" s="248"/>
-      <c r="U17" s="248"/>
-      <c r="V17" s="248"/>
-      <c r="W17" s="248"/>
-      <c r="X17" s="248"/>
-      <c r="Y17" s="248"/>
-      <c r="Z17" s="248"/>
-      <c r="AA17" s="248"/>
-      <c r="AB17" s="248"/>
-      <c r="AC17" s="248"/>
-      <c r="AD17" s="248"/>
-      <c r="AE17" s="248"/>
-      <c r="AF17" s="248"/>
-      <c r="AG17" s="248"/>
-      <c r="AH17" s="248"/>
-      <c r="AI17" s="248"/>
-      <c r="AJ17" s="248"/>
-      <c r="AK17" s="248"/>
-      <c r="AL17" s="248"/>
+      <c r="B17" s="249"/>
+      <c r="C17" s="249"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
+      <c r="J17" s="249"/>
+      <c r="K17" s="249"/>
+      <c r="L17" s="249"/>
+      <c r="M17" s="249"/>
+      <c r="N17" s="249"/>
+      <c r="O17" s="249"/>
+      <c r="P17" s="249"/>
+      <c r="Q17" s="249"/>
+      <c r="R17" s="249"/>
+      <c r="S17" s="249"/>
+      <c r="T17" s="249"/>
+      <c r="U17" s="249"/>
+      <c r="V17" s="249"/>
+      <c r="W17" s="249"/>
+      <c r="X17" s="249"/>
+      <c r="Y17" s="249"/>
+      <c r="Z17" s="249"/>
+      <c r="AA17" s="249"/>
+      <c r="AB17" s="249"/>
+      <c r="AC17" s="249"/>
+      <c r="AD17" s="249"/>
+      <c r="AE17" s="249"/>
+      <c r="AF17" s="249"/>
+      <c r="AG17" s="249"/>
+      <c r="AH17" s="249"/>
+      <c r="AI17" s="249"/>
+      <c r="AJ17" s="249"/>
+      <c r="AK17" s="249"/>
+      <c r="AL17" s="249"/>
     </row>
     <row r="18" spans="1:38" ht="18" customHeight="1">
-      <c r="A18" s="248" t="s">
+      <c r="A18" s="249" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="248"/>
-      <c r="C18" s="248"/>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
-      <c r="M18" s="248"/>
-      <c r="N18" s="248"/>
-      <c r="O18" s="248"/>
-      <c r="P18" s="248"/>
-      <c r="Q18" s="248"/>
-      <c r="R18" s="248"/>
-      <c r="S18" s="248"/>
-      <c r="T18" s="248"/>
-      <c r="U18" s="248"/>
-      <c r="V18" s="248"/>
-      <c r="W18" s="248"/>
-      <c r="X18" s="248"/>
-      <c r="Y18" s="248"/>
-      <c r="Z18" s="248"/>
-      <c r="AA18" s="248"/>
-      <c r="AB18" s="248"/>
-      <c r="AC18" s="248"/>
-      <c r="AD18" s="248"/>
-      <c r="AE18" s="248"/>
-      <c r="AF18" s="248"/>
-      <c r="AG18" s="248"/>
-      <c r="AH18" s="248"/>
-      <c r="AI18" s="248"/>
-      <c r="AJ18" s="248"/>
-      <c r="AK18" s="248"/>
-      <c r="AL18" s="248"/>
+      <c r="B18" s="249"/>
+      <c r="C18" s="249"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+      <c r="K18" s="249"/>
+      <c r="L18" s="249"/>
+      <c r="M18" s="249"/>
+      <c r="N18" s="249"/>
+      <c r="O18" s="249"/>
+      <c r="P18" s="249"/>
+      <c r="Q18" s="249"/>
+      <c r="R18" s="249"/>
+      <c r="S18" s="249"/>
+      <c r="T18" s="249"/>
+      <c r="U18" s="249"/>
+      <c r="V18" s="249"/>
+      <c r="W18" s="249"/>
+      <c r="X18" s="249"/>
+      <c r="Y18" s="249"/>
+      <c r="Z18" s="249"/>
+      <c r="AA18" s="249"/>
+      <c r="AB18" s="249"/>
+      <c r="AC18" s="249"/>
+      <c r="AD18" s="249"/>
+      <c r="AE18" s="249"/>
+      <c r="AF18" s="249"/>
+      <c r="AG18" s="249"/>
+      <c r="AH18" s="249"/>
+      <c r="AI18" s="249"/>
+      <c r="AJ18" s="249"/>
+      <c r="AK18" s="249"/>
+      <c r="AL18" s="249"/>
     </row>
     <row r="19" spans="1:38" ht="18" customHeight="1">
-      <c r="A19" s="248" t="s">
+      <c r="A19" s="249" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="248"/>
-      <c r="C19" s="248"/>
-      <c r="D19" s="248"/>
-      <c r="E19" s="248"/>
-      <c r="F19" s="248"/>
-      <c r="G19" s="248"/>
-      <c r="H19" s="248"/>
-      <c r="I19" s="248"/>
-      <c r="J19" s="248"/>
-      <c r="K19" s="248"/>
-      <c r="L19" s="248"/>
-      <c r="M19" s="248"/>
-      <c r="N19" s="248"/>
-      <c r="O19" s="248"/>
-      <c r="P19" s="248"/>
-      <c r="Q19" s="248"/>
-      <c r="R19" s="248"/>
-      <c r="S19" s="248"/>
-      <c r="T19" s="248"/>
-      <c r="U19" s="248"/>
-      <c r="V19" s="248"/>
-      <c r="W19" s="248"/>
-      <c r="X19" s="248"/>
-      <c r="Y19" s="248"/>
-      <c r="Z19" s="248"/>
-      <c r="AA19" s="248"/>
-      <c r="AB19" s="248"/>
-      <c r="AC19" s="248"/>
-      <c r="AD19" s="248"/>
-      <c r="AE19" s="248"/>
-      <c r="AF19" s="248"/>
-      <c r="AG19" s="248"/>
-      <c r="AH19" s="248"/>
-      <c r="AI19" s="248"/>
-      <c r="AJ19" s="248"/>
-      <c r="AK19" s="248"/>
-      <c r="AL19" s="248"/>
+      <c r="B19" s="249"/>
+      <c r="C19" s="249"/>
+      <c r="D19" s="249"/>
+      <c r="E19" s="249"/>
+      <c r="F19" s="249"/>
+      <c r="G19" s="249"/>
+      <c r="H19" s="249"/>
+      <c r="I19" s="249"/>
+      <c r="J19" s="249"/>
+      <c r="K19" s="249"/>
+      <c r="L19" s="249"/>
+      <c r="M19" s="249"/>
+      <c r="N19" s="249"/>
+      <c r="O19" s="249"/>
+      <c r="P19" s="249"/>
+      <c r="Q19" s="249"/>
+      <c r="R19" s="249"/>
+      <c r="S19" s="249"/>
+      <c r="T19" s="249"/>
+      <c r="U19" s="249"/>
+      <c r="V19" s="249"/>
+      <c r="W19" s="249"/>
+      <c r="X19" s="249"/>
+      <c r="Y19" s="249"/>
+      <c r="Z19" s="249"/>
+      <c r="AA19" s="249"/>
+      <c r="AB19" s="249"/>
+      <c r="AC19" s="249"/>
+      <c r="AD19" s="249"/>
+      <c r="AE19" s="249"/>
+      <c r="AF19" s="249"/>
+      <c r="AG19" s="249"/>
+      <c r="AH19" s="249"/>
+      <c r="AI19" s="249"/>
+      <c r="AJ19" s="249"/>
+      <c r="AK19" s="249"/>
+      <c r="AL19" s="249"/>
     </row>
     <row r="20" spans="1:38" ht="18" customHeight="1">
-      <c r="A20" s="248" t="s">
+      <c r="A20" s="249" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="248"/>
-      <c r="C20" s="248"/>
-      <c r="D20" s="248"/>
-      <c r="E20" s="248"/>
-      <c r="F20" s="248"/>
-      <c r="G20" s="248"/>
-      <c r="H20" s="248"/>
-      <c r="I20" s="248"/>
-      <c r="J20" s="248"/>
-      <c r="K20" s="248"/>
-      <c r="L20" s="248"/>
-      <c r="M20" s="248"/>
-      <c r="N20" s="248"/>
-      <c r="O20" s="248"/>
-      <c r="P20" s="248"/>
-      <c r="Q20" s="248"/>
-      <c r="R20" s="248"/>
-      <c r="S20" s="248"/>
-      <c r="T20" s="248"/>
-      <c r="U20" s="248"/>
-      <c r="V20" s="248"/>
-      <c r="W20" s="248"/>
-      <c r="X20" s="248"/>
-      <c r="Y20" s="248"/>
-      <c r="Z20" s="248"/>
-      <c r="AA20" s="248"/>
-      <c r="AB20" s="248"/>
-      <c r="AC20" s="248"/>
-      <c r="AD20" s="248"/>
-      <c r="AE20" s="248"/>
-      <c r="AF20" s="248"/>
-      <c r="AG20" s="248"/>
-      <c r="AH20" s="248"/>
-      <c r="AI20" s="248"/>
-      <c r="AJ20" s="248"/>
-      <c r="AK20" s="248"/>
-      <c r="AL20" s="248"/>
+      <c r="B20" s="249"/>
+      <c r="C20" s="249"/>
+      <c r="D20" s="249"/>
+      <c r="E20" s="249"/>
+      <c r="F20" s="249"/>
+      <c r="G20" s="249"/>
+      <c r="H20" s="249"/>
+      <c r="I20" s="249"/>
+      <c r="J20" s="249"/>
+      <c r="K20" s="249"/>
+      <c r="L20" s="249"/>
+      <c r="M20" s="249"/>
+      <c r="N20" s="249"/>
+      <c r="O20" s="249"/>
+      <c r="P20" s="249"/>
+      <c r="Q20" s="249"/>
+      <c r="R20" s="249"/>
+      <c r="S20" s="249"/>
+      <c r="T20" s="249"/>
+      <c r="U20" s="249"/>
+      <c r="V20" s="249"/>
+      <c r="W20" s="249"/>
+      <c r="X20" s="249"/>
+      <c r="Y20" s="249"/>
+      <c r="Z20" s="249"/>
+      <c r="AA20" s="249"/>
+      <c r="AB20" s="249"/>
+      <c r="AC20" s="249"/>
+      <c r="AD20" s="249"/>
+      <c r="AE20" s="249"/>
+      <c r="AF20" s="249"/>
+      <c r="AG20" s="249"/>
+      <c r="AH20" s="249"/>
+      <c r="AI20" s="249"/>
+      <c r="AJ20" s="249"/>
+      <c r="AK20" s="249"/>
+      <c r="AL20" s="249"/>
     </row>
     <row r="21" spans="1:38" ht="18" customHeight="1">
-      <c r="A21" s="248" t="s">
+      <c r="A21" s="249" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="248"/>
-      <c r="C21" s="248"/>
-      <c r="D21" s="248"/>
-      <c r="E21" s="248"/>
-      <c r="F21" s="248"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
-      <c r="I21" s="248"/>
-      <c r="J21" s="248"/>
-      <c r="K21" s="248"/>
-      <c r="L21" s="248"/>
-      <c r="M21" s="248"/>
-      <c r="N21" s="248"/>
-      <c r="O21" s="248"/>
-      <c r="P21" s="248"/>
-      <c r="Q21" s="248"/>
-      <c r="R21" s="248"/>
-      <c r="S21" s="248"/>
-      <c r="T21" s="248"/>
-      <c r="U21" s="248"/>
-      <c r="V21" s="248"/>
-      <c r="W21" s="248"/>
-      <c r="X21" s="248"/>
-      <c r="Y21" s="248"/>
-      <c r="Z21" s="248"/>
-      <c r="AA21" s="248"/>
-      <c r="AB21" s="248"/>
-      <c r="AC21" s="248"/>
-      <c r="AD21" s="248"/>
-      <c r="AE21" s="248"/>
-      <c r="AF21" s="248"/>
-      <c r="AG21" s="248"/>
-      <c r="AH21" s="248"/>
-      <c r="AI21" s="248"/>
-      <c r="AJ21" s="248"/>
-      <c r="AK21" s="248"/>
-      <c r="AL21" s="248"/>
+      <c r="B21" s="249"/>
+      <c r="C21" s="249"/>
+      <c r="D21" s="249"/>
+      <c r="E21" s="249"/>
+      <c r="F21" s="249"/>
+      <c r="G21" s="249"/>
+      <c r="H21" s="249"/>
+      <c r="I21" s="249"/>
+      <c r="J21" s="249"/>
+      <c r="K21" s="249"/>
+      <c r="L21" s="249"/>
+      <c r="M21" s="249"/>
+      <c r="N21" s="249"/>
+      <c r="O21" s="249"/>
+      <c r="P21" s="249"/>
+      <c r="Q21" s="249"/>
+      <c r="R21" s="249"/>
+      <c r="S21" s="249"/>
+      <c r="T21" s="249"/>
+      <c r="U21" s="249"/>
+      <c r="V21" s="249"/>
+      <c r="W21" s="249"/>
+      <c r="X21" s="249"/>
+      <c r="Y21" s="249"/>
+      <c r="Z21" s="249"/>
+      <c r="AA21" s="249"/>
+      <c r="AB21" s="249"/>
+      <c r="AC21" s="249"/>
+      <c r="AD21" s="249"/>
+      <c r="AE21" s="249"/>
+      <c r="AF21" s="249"/>
+      <c r="AG21" s="249"/>
+      <c r="AH21" s="249"/>
+      <c r="AI21" s="249"/>
+      <c r="AJ21" s="249"/>
+      <c r="AK21" s="249"/>
+      <c r="AL21" s="249"/>
     </row>
     <row r="22" spans="1:38" ht="18" customHeight="1">
-      <c r="A22" s="248" t="s">
+      <c r="A22" s="249" t="s">
         <v>123</v>
       </c>
-      <c r="B22" s="248"/>
-      <c r="C22" s="248"/>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="248"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
-      <c r="I22" s="248"/>
-      <c r="J22" s="248"/>
-      <c r="K22" s="248"/>
-      <c r="L22" s="248"/>
-      <c r="M22" s="248"/>
-      <c r="N22" s="248"/>
-      <c r="O22" s="248"/>
-      <c r="P22" s="248"/>
-      <c r="Q22" s="248"/>
-      <c r="R22" s="248"/>
-      <c r="S22" s="248"/>
-      <c r="T22" s="248"/>
-      <c r="U22" s="248"/>
-      <c r="V22" s="248"/>
-      <c r="W22" s="248"/>
-      <c r="X22" s="248"/>
-      <c r="Y22" s="248"/>
-      <c r="Z22" s="248"/>
-      <c r="AA22" s="248"/>
-      <c r="AB22" s="248"/>
-      <c r="AC22" s="248"/>
-      <c r="AD22" s="248"/>
-      <c r="AE22" s="248"/>
-      <c r="AF22" s="248"/>
-      <c r="AG22" s="248"/>
-      <c r="AH22" s="248"/>
-      <c r="AI22" s="248"/>
-      <c r="AJ22" s="248"/>
-      <c r="AK22" s="248"/>
-      <c r="AL22" s="248"/>
+      <c r="B22" s="249"/>
+      <c r="C22" s="249"/>
+      <c r="D22" s="249"/>
+      <c r="E22" s="249"/>
+      <c r="F22" s="249"/>
+      <c r="G22" s="249"/>
+      <c r="H22" s="249"/>
+      <c r="I22" s="249"/>
+      <c r="J22" s="249"/>
+      <c r="K22" s="249"/>
+      <c r="L22" s="249"/>
+      <c r="M22" s="249"/>
+      <c r="N22" s="249"/>
+      <c r="O22" s="249"/>
+      <c r="P22" s="249"/>
+      <c r="Q22" s="249"/>
+      <c r="R22" s="249"/>
+      <c r="S22" s="249"/>
+      <c r="T22" s="249"/>
+      <c r="U22" s="249"/>
+      <c r="V22" s="249"/>
+      <c r="W22" s="249"/>
+      <c r="X22" s="249"/>
+      <c r="Y22" s="249"/>
+      <c r="Z22" s="249"/>
+      <c r="AA22" s="249"/>
+      <c r="AB22" s="249"/>
+      <c r="AC22" s="249"/>
+      <c r="AD22" s="249"/>
+      <c r="AE22" s="249"/>
+      <c r="AF22" s="249"/>
+      <c r="AG22" s="249"/>
+      <c r="AH22" s="249"/>
+      <c r="AI22" s="249"/>
+      <c r="AJ22" s="249"/>
+      <c r="AK22" s="249"/>
+      <c r="AL22" s="249"/>
     </row>
     <row r="23" spans="1:38" ht="14.4">
       <c r="A23" s="6" t="s">
@@ -19187,7 +19624,7 @@
     </row>
     <row r="25" spans="1:38">
       <c r="A25" s="179" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B25" s="179"/>
       <c r="C25" s="179"/>
@@ -19286,17 +19723,17 @@
     </row>
     <row r="29" spans="1:38">
       <c r="A29" s="108" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30" spans="1:38">
       <c r="A30" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G30" s="143"/>
       <c r="H30" s="143"/>
       <c r="I30" s="109" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AJ30" s="143"/>
       <c r="AK30" s="143"/>
@@ -19304,7 +19741,7 @@
     </row>
     <row r="31" spans="1:38">
       <c r="A31" s="22" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q31" s="143"/>
       <c r="R31" s="143"/>
@@ -19320,12 +19757,12 @@
       <c r="AB31" s="143"/>
       <c r="AC31" s="143"/>
       <c r="AD31" s="110" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="109" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B32" s="109"/>
       <c r="C32" s="109"/>
@@ -19346,7 +19783,7 @@
       <c r="R32" s="232"/>
       <c r="S32" s="232"/>
       <c r="T32" s="22" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="U32" s="143"/>
       <c r="V32" s="143"/>
@@ -19355,7 +19792,7 @@
       <c r="Y32" s="143"/>
       <c r="Z32" s="143"/>
       <c r="AA32" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AB32" s="111"/>
       <c r="AC32" s="111"/>
@@ -19369,48 +19806,48 @@
       <c r="AL32"/>
     </row>
     <row r="33" spans="1:38">
-      <c r="A33" s="249"/>
-      <c r="B33" s="249"/>
-      <c r="C33" s="249"/>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="249"/>
-      <c r="I33" s="249"/>
-      <c r="J33" s="249"/>
-      <c r="K33" s="249"/>
-      <c r="L33" s="249"/>
-      <c r="M33" s="249"/>
-      <c r="N33" s="249"/>
-      <c r="O33" s="249"/>
-      <c r="P33" s="249"/>
-      <c r="Q33" s="249"/>
-      <c r="R33" s="249"/>
-      <c r="S33" s="249"/>
-      <c r="T33" s="249"/>
-      <c r="U33" s="249"/>
-      <c r="V33" s="249"/>
-      <c r="W33" s="249"/>
-      <c r="X33" s="249"/>
-      <c r="Y33" s="249"/>
-      <c r="Z33" s="249"/>
-      <c r="AA33" s="249"/>
-      <c r="AB33" s="249"/>
-      <c r="AC33" s="249"/>
-      <c r="AD33" s="249"/>
-      <c r="AE33" s="249"/>
-      <c r="AF33" s="249"/>
-      <c r="AG33" s="249"/>
-      <c r="AH33" s="249"/>
-      <c r="AI33" s="249"/>
-      <c r="AJ33" s="249"/>
-      <c r="AK33" s="249"/>
-      <c r="AL33" s="249"/>
+      <c r="A33" s="246"/>
+      <c r="B33" s="246"/>
+      <c r="C33" s="246"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
+      <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="246"/>
+      <c r="L33" s="246"/>
+      <c r="M33" s="246"/>
+      <c r="N33" s="246"/>
+      <c r="O33" s="246"/>
+      <c r="P33" s="246"/>
+      <c r="Q33" s="246"/>
+      <c r="R33" s="246"/>
+      <c r="S33" s="246"/>
+      <c r="T33" s="246"/>
+      <c r="U33" s="246"/>
+      <c r="V33" s="246"/>
+      <c r="W33" s="246"/>
+      <c r="X33" s="246"/>
+      <c r="Y33" s="246"/>
+      <c r="Z33" s="246"/>
+      <c r="AA33" s="246"/>
+      <c r="AB33" s="246"/>
+      <c r="AC33" s="246"/>
+      <c r="AD33" s="246"/>
+      <c r="AE33" s="246"/>
+      <c r="AF33" s="246"/>
+      <c r="AG33" s="246"/>
+      <c r="AH33" s="246"/>
+      <c r="AI33" s="246"/>
+      <c r="AJ33" s="246"/>
+      <c r="AK33" s="246"/>
+      <c r="AL33" s="246"/>
     </row>
     <row r="34" spans="1:38">
       <c r="A34" s="114" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B34" s="113"/>
       <c r="C34" s="113"/>
@@ -19437,7 +19874,7 @@
     </row>
     <row r="35" spans="1:38">
       <c r="A35" s="109" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B35" s="109"/>
       <c r="C35" s="109"/>
@@ -19455,7 +19892,7 @@
       <c r="O35" s="143"/>
       <c r="P35" s="143"/>
       <c r="Q35" s="72" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="R35" s="116"/>
       <c r="S35" s="116"/>
@@ -19475,6 +19912,21 @@
     <mergeCell ref="U32:Z32"/>
     <mergeCell ref="U10:Z10"/>
     <mergeCell ref="AA10:AF10"/>
+    <mergeCell ref="AG13:AL13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="U14:Z14"/>
+    <mergeCell ref="AA14:AF14"/>
+    <mergeCell ref="AG14:AL14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="U13:Z13"/>
+    <mergeCell ref="AA13:AF13"/>
+    <mergeCell ref="AG16:AL16"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="I15:N15"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="F5:K5"/>
@@ -19497,21 +19949,6 @@
     <mergeCell ref="U12:Z12"/>
     <mergeCell ref="AA12:AF12"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="AG13:AL13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="U14:Z14"/>
-    <mergeCell ref="AA14:AF14"/>
-    <mergeCell ref="AG14:AL14"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="U13:Z13"/>
-    <mergeCell ref="AA13:AF13"/>
-    <mergeCell ref="AG16:AL16"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I15:N15"/>
     <mergeCell ref="O15:T15"/>
     <mergeCell ref="U15:Z15"/>
     <mergeCell ref="AA15:AF15"/>
@@ -19637,7 +20074,7 @@
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
@@ -19756,7 +20193,7 @@
     </row>
     <row r="5" spans="1:38" ht="15.6">
       <c r="A5" s="107" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -19797,7 +20234,7 @@
     </row>
     <row r="6" spans="1:38" ht="15.6">
       <c r="A6" s="107" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B6" s="28"/>
       <c r="C6" s="28"/>
@@ -19830,12 +20267,12 @@
       <c r="AD6" s="28"/>
       <c r="AE6" s="28"/>
       <c r="AF6" s="28"/>
-      <c r="AG6" s="275"/>
-      <c r="AH6" s="275"/>
-      <c r="AI6" s="275"/>
-      <c r="AJ6" s="275"/>
-      <c r="AK6" s="275"/>
-      <c r="AL6" s="275"/>
+      <c r="AG6" s="271"/>
+      <c r="AH6" s="271"/>
+      <c r="AI6" s="271"/>
+      <c r="AJ6" s="271"/>
+      <c r="AK6" s="271"/>
+      <c r="AL6" s="271"/>
     </row>
     <row r="7" spans="1:38">
       <c r="A7" s="28"/>
@@ -19879,7 +20316,7 @@
     </row>
     <row r="8" spans="1:38" ht="15.6">
       <c r="A8" s="107" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B8" s="107"/>
       <c r="C8" s="107"/>
@@ -19921,7 +20358,7 @@
     </row>
     <row r="9" spans="1:38" ht="15.6">
       <c r="A9" s="107" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B9" s="107"/>
       <c r="C9" s="107"/>
@@ -20002,18 +20439,18 @@
       <c r="AL10" s="28"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1">
-      <c r="A11" s="248" t="s">
+      <c r="A11" s="249" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="248"/>
-      <c r="C11" s="248"/>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
+      <c r="B11" s="249"/>
+      <c r="C11" s="249"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
       <c r="I11" s="276" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J11" s="276"/>
       <c r="K11" s="276"/>
@@ -20050,14 +20487,14 @@
       <c r="AL11" s="276"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
-      <c r="A12" s="248"/>
-      <c r="B12" s="248"/>
-      <c r="C12" s="248"/>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="248"/>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
+      <c r="A12" s="249"/>
+      <c r="B12" s="249"/>
+      <c r="C12" s="249"/>
+      <c r="D12" s="249"/>
+      <c r="E12" s="249"/>
+      <c r="F12" s="249"/>
+      <c r="G12" s="249"/>
+      <c r="H12" s="249"/>
       <c r="I12" s="276"/>
       <c r="J12" s="276"/>
       <c r="K12" s="276"/>
@@ -20090,14 +20527,14 @@
       <c r="AL12" s="276"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
-      <c r="A13" s="248"/>
-      <c r="B13" s="248"/>
-      <c r="C13" s="248"/>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
+      <c r="A13" s="249"/>
+      <c r="B13" s="249"/>
+      <c r="C13" s="249"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="249"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="249"/>
       <c r="I13" s="276"/>
       <c r="J13" s="276"/>
       <c r="K13" s="276"/>
@@ -20141,7 +20578,7 @@
     </row>
     <row r="14" spans="1:38" ht="18" customHeight="1">
       <c r="A14" s="276" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B14" s="276"/>
       <c r="C14" s="276"/>
@@ -20151,37 +20588,37 @@
       <c r="G14" s="276"/>
       <c r="H14" s="276"/>
       <c r="I14" s="276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J14" s="276"/>
       <c r="K14" s="276"/>
       <c r="L14" s="276"/>
-      <c r="M14" s="271"/>
-      <c r="N14" s="271"/>
-      <c r="O14" s="271"/>
-      <c r="P14" s="271"/>
-      <c r="Q14" s="271"/>
-      <c r="R14" s="271"/>
-      <c r="S14" s="271"/>
-      <c r="T14" s="271"/>
-      <c r="U14" s="271"/>
-      <c r="V14" s="271"/>
-      <c r="W14" s="271"/>
-      <c r="X14" s="271"/>
-      <c r="Y14" s="271"/>
-      <c r="Z14" s="271"/>
-      <c r="AA14" s="271"/>
-      <c r="AB14" s="271"/>
-      <c r="AC14" s="271"/>
-      <c r="AD14" s="271"/>
-      <c r="AE14" s="271"/>
-      <c r="AF14" s="271"/>
-      <c r="AG14" s="271"/>
-      <c r="AH14" s="271"/>
-      <c r="AI14" s="271"/>
-      <c r="AJ14" s="271"/>
-      <c r="AK14" s="271"/>
-      <c r="AL14" s="271"/>
+      <c r="M14" s="272"/>
+      <c r="N14" s="272"/>
+      <c r="O14" s="272"/>
+      <c r="P14" s="272"/>
+      <c r="Q14" s="272"/>
+      <c r="R14" s="272"/>
+      <c r="S14" s="272"/>
+      <c r="T14" s="272"/>
+      <c r="U14" s="272"/>
+      <c r="V14" s="272"/>
+      <c r="W14" s="272"/>
+      <c r="X14" s="272"/>
+      <c r="Y14" s="272"/>
+      <c r="Z14" s="272"/>
+      <c r="AA14" s="272"/>
+      <c r="AB14" s="272"/>
+      <c r="AC14" s="272"/>
+      <c r="AD14" s="272"/>
+      <c r="AE14" s="272"/>
+      <c r="AF14" s="272"/>
+      <c r="AG14" s="272"/>
+      <c r="AH14" s="272"/>
+      <c r="AI14" s="272"/>
+      <c r="AJ14" s="272"/>
+      <c r="AK14" s="272"/>
+      <c r="AL14" s="272"/>
     </row>
     <row r="15" spans="1:38" ht="18" customHeight="1">
       <c r="A15" s="276"/>
@@ -20193,37 +20630,37 @@
       <c r="G15" s="276"/>
       <c r="H15" s="276"/>
       <c r="I15" s="276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J15" s="276"/>
       <c r="K15" s="276"/>
       <c r="L15" s="276"/>
-      <c r="M15" s="271"/>
-      <c r="N15" s="271"/>
-      <c r="O15" s="271"/>
-      <c r="P15" s="271"/>
-      <c r="Q15" s="271"/>
-      <c r="R15" s="271"/>
-      <c r="S15" s="271"/>
-      <c r="T15" s="271"/>
-      <c r="U15" s="271"/>
-      <c r="V15" s="271"/>
-      <c r="W15" s="271"/>
-      <c r="X15" s="271"/>
-      <c r="Y15" s="271"/>
-      <c r="Z15" s="271"/>
-      <c r="AA15" s="271"/>
-      <c r="AB15" s="271"/>
-      <c r="AC15" s="271"/>
-      <c r="AD15" s="271"/>
-      <c r="AE15" s="271"/>
-      <c r="AF15" s="271"/>
-      <c r="AG15" s="271"/>
-      <c r="AH15" s="271"/>
-      <c r="AI15" s="271"/>
-      <c r="AJ15" s="271"/>
-      <c r="AK15" s="271"/>
-      <c r="AL15" s="271"/>
+      <c r="M15" s="272"/>
+      <c r="N15" s="272"/>
+      <c r="O15" s="272"/>
+      <c r="P15" s="272"/>
+      <c r="Q15" s="272"/>
+      <c r="R15" s="272"/>
+      <c r="S15" s="272"/>
+      <c r="T15" s="272"/>
+      <c r="U15" s="272"/>
+      <c r="V15" s="272"/>
+      <c r="W15" s="272"/>
+      <c r="X15" s="272"/>
+      <c r="Y15" s="272"/>
+      <c r="Z15" s="272"/>
+      <c r="AA15" s="272"/>
+      <c r="AB15" s="272"/>
+      <c r="AC15" s="272"/>
+      <c r="AD15" s="272"/>
+      <c r="AE15" s="272"/>
+      <c r="AF15" s="272"/>
+      <c r="AG15" s="272"/>
+      <c r="AH15" s="272"/>
+      <c r="AI15" s="272"/>
+      <c r="AJ15" s="272"/>
+      <c r="AK15" s="272"/>
+      <c r="AL15" s="272"/>
     </row>
     <row r="16" spans="1:38" ht="18" customHeight="1">
       <c r="A16" s="276"/>
@@ -20235,37 +20672,37 @@
       <c r="G16" s="276"/>
       <c r="H16" s="276"/>
       <c r="I16" s="276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J16" s="276"/>
       <c r="K16" s="276"/>
       <c r="L16" s="276"/>
-      <c r="M16" s="271"/>
-      <c r="N16" s="271"/>
-      <c r="O16" s="271"/>
-      <c r="P16" s="271"/>
-      <c r="Q16" s="271"/>
-      <c r="R16" s="271"/>
-      <c r="S16" s="271"/>
-      <c r="T16" s="271"/>
-      <c r="U16" s="271"/>
-      <c r="V16" s="271"/>
-      <c r="W16" s="271"/>
-      <c r="X16" s="271"/>
-      <c r="Y16" s="271"/>
-      <c r="Z16" s="271"/>
-      <c r="AA16" s="271"/>
-      <c r="AB16" s="271"/>
-      <c r="AC16" s="271"/>
-      <c r="AD16" s="271"/>
-      <c r="AE16" s="271"/>
-      <c r="AF16" s="271"/>
-      <c r="AG16" s="271"/>
-      <c r="AH16" s="271"/>
-      <c r="AI16" s="271"/>
-      <c r="AJ16" s="271"/>
-      <c r="AK16" s="271"/>
-      <c r="AL16" s="271"/>
+      <c r="M16" s="272"/>
+      <c r="N16" s="272"/>
+      <c r="O16" s="272"/>
+      <c r="P16" s="272"/>
+      <c r="Q16" s="272"/>
+      <c r="R16" s="272"/>
+      <c r="S16" s="272"/>
+      <c r="T16" s="272"/>
+      <c r="U16" s="272"/>
+      <c r="V16" s="272"/>
+      <c r="W16" s="272"/>
+      <c r="X16" s="272"/>
+      <c r="Y16" s="272"/>
+      <c r="Z16" s="272"/>
+      <c r="AA16" s="272"/>
+      <c r="AB16" s="272"/>
+      <c r="AC16" s="272"/>
+      <c r="AD16" s="272"/>
+      <c r="AE16" s="272"/>
+      <c r="AF16" s="272"/>
+      <c r="AG16" s="272"/>
+      <c r="AH16" s="272"/>
+      <c r="AI16" s="272"/>
+      <c r="AJ16" s="272"/>
+      <c r="AK16" s="272"/>
+      <c r="AL16" s="272"/>
     </row>
     <row r="17" spans="1:38" ht="18" customHeight="1">
       <c r="A17" s="276"/>
@@ -20277,41 +20714,41 @@
       <c r="G17" s="276"/>
       <c r="H17" s="276"/>
       <c r="I17" s="276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J17" s="276"/>
       <c r="K17" s="276"/>
       <c r="L17" s="276"/>
-      <c r="M17" s="271"/>
-      <c r="N17" s="271"/>
-      <c r="O17" s="271"/>
-      <c r="P17" s="271"/>
-      <c r="Q17" s="271"/>
-      <c r="R17" s="271"/>
-      <c r="S17" s="271"/>
-      <c r="T17" s="271"/>
-      <c r="U17" s="271"/>
-      <c r="V17" s="271"/>
-      <c r="W17" s="271"/>
-      <c r="X17" s="271"/>
-      <c r="Y17" s="271"/>
-      <c r="Z17" s="271"/>
-      <c r="AA17" s="271"/>
-      <c r="AB17" s="271"/>
-      <c r="AC17" s="271"/>
-      <c r="AD17" s="271"/>
-      <c r="AE17" s="271"/>
-      <c r="AF17" s="271"/>
-      <c r="AG17" s="271"/>
-      <c r="AH17" s="271"/>
-      <c r="AI17" s="271"/>
-      <c r="AJ17" s="271"/>
-      <c r="AK17" s="271"/>
-      <c r="AL17" s="271"/>
+      <c r="M17" s="272"/>
+      <c r="N17" s="272"/>
+      <c r="O17" s="272"/>
+      <c r="P17" s="272"/>
+      <c r="Q17" s="272"/>
+      <c r="R17" s="272"/>
+      <c r="S17" s="272"/>
+      <c r="T17" s="272"/>
+      <c r="U17" s="272"/>
+      <c r="V17" s="272"/>
+      <c r="W17" s="272"/>
+      <c r="X17" s="272"/>
+      <c r="Y17" s="272"/>
+      <c r="Z17" s="272"/>
+      <c r="AA17" s="272"/>
+      <c r="AB17" s="272"/>
+      <c r="AC17" s="272"/>
+      <c r="AD17" s="272"/>
+      <c r="AE17" s="272"/>
+      <c r="AF17" s="272"/>
+      <c r="AG17" s="272"/>
+      <c r="AH17" s="272"/>
+      <c r="AI17" s="272"/>
+      <c r="AJ17" s="272"/>
+      <c r="AK17" s="272"/>
+      <c r="AL17" s="272"/>
     </row>
     <row r="18" spans="1:38" ht="18" customHeight="1">
       <c r="A18" s="276" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B18" s="276"/>
       <c r="C18" s="276"/>
@@ -20321,37 +20758,37 @@
       <c r="G18" s="276"/>
       <c r="H18" s="276"/>
       <c r="I18" s="276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J18" s="276"/>
       <c r="K18" s="276"/>
       <c r="L18" s="276"/>
-      <c r="M18" s="271"/>
-      <c r="N18" s="271"/>
-      <c r="O18" s="271"/>
-      <c r="P18" s="271"/>
-      <c r="Q18" s="271"/>
-      <c r="R18" s="271"/>
-      <c r="S18" s="271"/>
-      <c r="T18" s="271"/>
-      <c r="U18" s="271"/>
-      <c r="V18" s="271"/>
-      <c r="W18" s="271"/>
-      <c r="X18" s="271"/>
-      <c r="Y18" s="271"/>
-      <c r="Z18" s="271"/>
-      <c r="AA18" s="271"/>
-      <c r="AB18" s="271"/>
-      <c r="AC18" s="271"/>
-      <c r="AD18" s="271"/>
-      <c r="AE18" s="271"/>
-      <c r="AF18" s="271"/>
-      <c r="AG18" s="271"/>
-      <c r="AH18" s="271"/>
-      <c r="AI18" s="271"/>
-      <c r="AJ18" s="271"/>
-      <c r="AK18" s="271"/>
-      <c r="AL18" s="271"/>
+      <c r="M18" s="272"/>
+      <c r="N18" s="272"/>
+      <c r="O18" s="272"/>
+      <c r="P18" s="272"/>
+      <c r="Q18" s="272"/>
+      <c r="R18" s="272"/>
+      <c r="S18" s="272"/>
+      <c r="T18" s="272"/>
+      <c r="U18" s="272"/>
+      <c r="V18" s="272"/>
+      <c r="W18" s="272"/>
+      <c r="X18" s="272"/>
+      <c r="Y18" s="272"/>
+      <c r="Z18" s="272"/>
+      <c r="AA18" s="272"/>
+      <c r="AB18" s="272"/>
+      <c r="AC18" s="272"/>
+      <c r="AD18" s="272"/>
+      <c r="AE18" s="272"/>
+      <c r="AF18" s="272"/>
+      <c r="AG18" s="272"/>
+      <c r="AH18" s="272"/>
+      <c r="AI18" s="272"/>
+      <c r="AJ18" s="272"/>
+      <c r="AK18" s="272"/>
+      <c r="AL18" s="272"/>
     </row>
     <row r="19" spans="1:38" ht="18" customHeight="1">
       <c r="A19" s="276"/>
@@ -20363,37 +20800,37 @@
       <c r="G19" s="276"/>
       <c r="H19" s="276"/>
       <c r="I19" s="276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J19" s="276"/>
       <c r="K19" s="276"/>
       <c r="L19" s="276"/>
-      <c r="M19" s="271"/>
-      <c r="N19" s="271"/>
-      <c r="O19" s="271"/>
-      <c r="P19" s="271"/>
-      <c r="Q19" s="271"/>
-      <c r="R19" s="271"/>
-      <c r="S19" s="271"/>
-      <c r="T19" s="271"/>
-      <c r="U19" s="271"/>
-      <c r="V19" s="271"/>
-      <c r="W19" s="271"/>
-      <c r="X19" s="271"/>
-      <c r="Y19" s="271"/>
-      <c r="Z19" s="271"/>
-      <c r="AA19" s="271"/>
-      <c r="AB19" s="271"/>
-      <c r="AC19" s="271"/>
-      <c r="AD19" s="271"/>
-      <c r="AE19" s="271"/>
-      <c r="AF19" s="271"/>
-      <c r="AG19" s="271"/>
-      <c r="AH19" s="271"/>
-      <c r="AI19" s="271"/>
-      <c r="AJ19" s="271"/>
-      <c r="AK19" s="271"/>
-      <c r="AL19" s="271"/>
+      <c r="M19" s="272"/>
+      <c r="N19" s="272"/>
+      <c r="O19" s="272"/>
+      <c r="P19" s="272"/>
+      <c r="Q19" s="272"/>
+      <c r="R19" s="272"/>
+      <c r="S19" s="272"/>
+      <c r="T19" s="272"/>
+      <c r="U19" s="272"/>
+      <c r="V19" s="272"/>
+      <c r="W19" s="272"/>
+      <c r="X19" s="272"/>
+      <c r="Y19" s="272"/>
+      <c r="Z19" s="272"/>
+      <c r="AA19" s="272"/>
+      <c r="AB19" s="272"/>
+      <c r="AC19" s="272"/>
+      <c r="AD19" s="272"/>
+      <c r="AE19" s="272"/>
+      <c r="AF19" s="272"/>
+      <c r="AG19" s="272"/>
+      <c r="AH19" s="272"/>
+      <c r="AI19" s="272"/>
+      <c r="AJ19" s="272"/>
+      <c r="AK19" s="272"/>
+      <c r="AL19" s="272"/>
     </row>
     <row r="20" spans="1:38" ht="18" customHeight="1">
       <c r="A20" s="276"/>
@@ -20405,37 +20842,37 @@
       <c r="G20" s="276"/>
       <c r="H20" s="276"/>
       <c r="I20" s="276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J20" s="276"/>
       <c r="K20" s="276"/>
       <c r="L20" s="276"/>
-      <c r="M20" s="271"/>
-      <c r="N20" s="271"/>
-      <c r="O20" s="271"/>
-      <c r="P20" s="271"/>
-      <c r="Q20" s="271"/>
-      <c r="R20" s="271"/>
-      <c r="S20" s="271"/>
-      <c r="T20" s="271"/>
-      <c r="U20" s="271"/>
-      <c r="V20" s="271"/>
-      <c r="W20" s="271"/>
-      <c r="X20" s="271"/>
-      <c r="Y20" s="271"/>
-      <c r="Z20" s="271"/>
-      <c r="AA20" s="271"/>
-      <c r="AB20" s="271"/>
-      <c r="AC20" s="271"/>
-      <c r="AD20" s="271"/>
-      <c r="AE20" s="271"/>
-      <c r="AF20" s="271"/>
-      <c r="AG20" s="271"/>
-      <c r="AH20" s="271"/>
-      <c r="AI20" s="271"/>
-      <c r="AJ20" s="271"/>
-      <c r="AK20" s="271"/>
-      <c r="AL20" s="271"/>
+      <c r="M20" s="272"/>
+      <c r="N20" s="272"/>
+      <c r="O20" s="272"/>
+      <c r="P20" s="272"/>
+      <c r="Q20" s="272"/>
+      <c r="R20" s="272"/>
+      <c r="S20" s="272"/>
+      <c r="T20" s="272"/>
+      <c r="U20" s="272"/>
+      <c r="V20" s="272"/>
+      <c r="W20" s="272"/>
+      <c r="X20" s="272"/>
+      <c r="Y20" s="272"/>
+      <c r="Z20" s="272"/>
+      <c r="AA20" s="272"/>
+      <c r="AB20" s="272"/>
+      <c r="AC20" s="272"/>
+      <c r="AD20" s="272"/>
+      <c r="AE20" s="272"/>
+      <c r="AF20" s="272"/>
+      <c r="AG20" s="272"/>
+      <c r="AH20" s="272"/>
+      <c r="AI20" s="272"/>
+      <c r="AJ20" s="272"/>
+      <c r="AK20" s="272"/>
+      <c r="AL20" s="272"/>
     </row>
     <row r="21" spans="1:38" ht="18" customHeight="1">
       <c r="A21" s="276"/>
@@ -20447,41 +20884,41 @@
       <c r="G21" s="276"/>
       <c r="H21" s="276"/>
       <c r="I21" s="276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J21" s="276"/>
       <c r="K21" s="276"/>
       <c r="L21" s="276"/>
-      <c r="M21" s="271"/>
-      <c r="N21" s="271"/>
-      <c r="O21" s="271"/>
-      <c r="P21" s="271"/>
-      <c r="Q21" s="271"/>
-      <c r="R21" s="271"/>
-      <c r="S21" s="271"/>
-      <c r="T21" s="271"/>
-      <c r="U21" s="271"/>
-      <c r="V21" s="271"/>
-      <c r="W21" s="271"/>
-      <c r="X21" s="271"/>
-      <c r="Y21" s="271"/>
-      <c r="Z21" s="271"/>
-      <c r="AA21" s="271"/>
-      <c r="AB21" s="271"/>
-      <c r="AC21" s="271"/>
-      <c r="AD21" s="271"/>
-      <c r="AE21" s="271"/>
-      <c r="AF21" s="271"/>
-      <c r="AG21" s="271"/>
-      <c r="AH21" s="271"/>
-      <c r="AI21" s="271"/>
-      <c r="AJ21" s="271"/>
-      <c r="AK21" s="271"/>
-      <c r="AL21" s="271"/>
+      <c r="M21" s="272"/>
+      <c r="N21" s="272"/>
+      <c r="O21" s="272"/>
+      <c r="P21" s="272"/>
+      <c r="Q21" s="272"/>
+      <c r="R21" s="272"/>
+      <c r="S21" s="272"/>
+      <c r="T21" s="272"/>
+      <c r="U21" s="272"/>
+      <c r="V21" s="272"/>
+      <c r="W21" s="272"/>
+      <c r="X21" s="272"/>
+      <c r="Y21" s="272"/>
+      <c r="Z21" s="272"/>
+      <c r="AA21" s="272"/>
+      <c r="AB21" s="272"/>
+      <c r="AC21" s="272"/>
+      <c r="AD21" s="272"/>
+      <c r="AE21" s="272"/>
+      <c r="AF21" s="272"/>
+      <c r="AG21" s="272"/>
+      <c r="AH21" s="272"/>
+      <c r="AI21" s="272"/>
+      <c r="AJ21" s="272"/>
+      <c r="AK21" s="272"/>
+      <c r="AL21" s="272"/>
     </row>
     <row r="22" spans="1:38">
       <c r="A22" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:38">
@@ -20503,6 +20940,11 @@
     <mergeCell ref="AC21:AF21"/>
     <mergeCell ref="M18:P18"/>
     <mergeCell ref="M20:P20"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="M19:P19"/>
     <mergeCell ref="A14:H17"/>
     <mergeCell ref="A18:H21"/>
     <mergeCell ref="AG14:AL14"/>
@@ -20519,6 +20961,14 @@
     <mergeCell ref="AC19:AF19"/>
     <mergeCell ref="U21:X21"/>
     <mergeCell ref="Y21:AB21"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="Y14:AB14"/>
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="M15:P15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="U15:X15"/>
+    <mergeCell ref="Y15:AB15"/>
+    <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="AC16:AF16"/>
     <mergeCell ref="M17:P17"/>
@@ -20526,36 +20976,19 @@
     <mergeCell ref="U17:X17"/>
     <mergeCell ref="Y17:AB17"/>
     <mergeCell ref="AC17:AF17"/>
-    <mergeCell ref="Y14:AB14"/>
-    <mergeCell ref="AC14:AF14"/>
-    <mergeCell ref="M15:P15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="U15:X15"/>
-    <mergeCell ref="Y15:AB15"/>
-    <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="Q19:T19"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="U14:X14"/>
     <mergeCell ref="I17:L17"/>
     <mergeCell ref="I18:L18"/>
     <mergeCell ref="I19:L19"/>
     <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="Q16:T16"/>
     <mergeCell ref="U16:X16"/>
-    <mergeCell ref="I11:L13"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="I15:L15"/>
     <mergeCell ref="I16:L16"/>
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="M16:P16"/>
     <mergeCell ref="I14:L14"/>
     <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="M19:P19"/>
+    <mergeCell ref="I15:L15"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="AG6:AL6"/>
     <mergeCell ref="M1:AL1"/>
@@ -20564,6 +20997,10 @@
     <mergeCell ref="Y13:AB13"/>
     <mergeCell ref="AC13:AF13"/>
     <mergeCell ref="A11:H13"/>
+    <mergeCell ref="I11:L13"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="U13:X13"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -21123,17 +21560,17 @@
     </row>
     <row r="19" spans="1:38">
       <c r="A19" s="108" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:38">
       <c r="A20" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G20" s="143"/>
       <c r="H20" s="143"/>
       <c r="I20" s="109" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AJ20" s="143"/>
       <c r="AK20" s="143"/>
@@ -21141,7 +21578,7 @@
     </row>
     <row r="21" spans="1:38">
       <c r="A21" s="22" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q21" s="143"/>
       <c r="R21" s="143"/>
@@ -21157,12 +21594,12 @@
       <c r="AB21" s="143"/>
       <c r="AC21" s="143"/>
       <c r="AD21" s="110" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" spans="1:38">
       <c r="A22" s="109" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B22" s="109"/>
       <c r="C22" s="109"/>
@@ -21183,7 +21620,7 @@
       <c r="R22" s="232"/>
       <c r="S22" s="232"/>
       <c r="T22" s="22" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="U22" s="143"/>
       <c r="V22" s="143"/>
@@ -21192,7 +21629,7 @@
       <c r="Y22" s="143"/>
       <c r="Z22" s="143"/>
       <c r="AA22" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AB22" s="111"/>
       <c r="AC22" s="111"/>
@@ -21206,48 +21643,48 @@
       <c r="AL22"/>
     </row>
     <row r="23" spans="1:38">
-      <c r="A23" s="249"/>
-      <c r="B23" s="249"/>
-      <c r="C23" s="249"/>
-      <c r="D23" s="249"/>
-      <c r="E23" s="249"/>
-      <c r="F23" s="249"/>
-      <c r="G23" s="249"/>
-      <c r="H23" s="249"/>
-      <c r="I23" s="249"/>
-      <c r="J23" s="249"/>
-      <c r="K23" s="249"/>
-      <c r="L23" s="249"/>
-      <c r="M23" s="249"/>
-      <c r="N23" s="249"/>
-      <c r="O23" s="249"/>
-      <c r="P23" s="249"/>
-      <c r="Q23" s="249"/>
-      <c r="R23" s="249"/>
-      <c r="S23" s="249"/>
-      <c r="T23" s="249"/>
-      <c r="U23" s="249"/>
-      <c r="V23" s="249"/>
-      <c r="W23" s="249"/>
-      <c r="X23" s="249"/>
-      <c r="Y23" s="249"/>
-      <c r="Z23" s="249"/>
-      <c r="AA23" s="249"/>
-      <c r="AB23" s="249"/>
-      <c r="AC23" s="249"/>
-      <c r="AD23" s="249"/>
-      <c r="AE23" s="249"/>
-      <c r="AF23" s="249"/>
-      <c r="AG23" s="249"/>
-      <c r="AH23" s="249"/>
-      <c r="AI23" s="249"/>
-      <c r="AJ23" s="249"/>
-      <c r="AK23" s="249"/>
-      <c r="AL23" s="249"/>
+      <c r="A23" s="246"/>
+      <c r="B23" s="246"/>
+      <c r="C23" s="246"/>
+      <c r="D23" s="246"/>
+      <c r="E23" s="246"/>
+      <c r="F23" s="246"/>
+      <c r="G23" s="246"/>
+      <c r="H23" s="246"/>
+      <c r="I23" s="246"/>
+      <c r="J23" s="246"/>
+      <c r="K23" s="246"/>
+      <c r="L23" s="246"/>
+      <c r="M23" s="246"/>
+      <c r="N23" s="246"/>
+      <c r="O23" s="246"/>
+      <c r="P23" s="246"/>
+      <c r="Q23" s="246"/>
+      <c r="R23" s="246"/>
+      <c r="S23" s="246"/>
+      <c r="T23" s="246"/>
+      <c r="U23" s="246"/>
+      <c r="V23" s="246"/>
+      <c r="W23" s="246"/>
+      <c r="X23" s="246"/>
+      <c r="Y23" s="246"/>
+      <c r="Z23" s="246"/>
+      <c r="AA23" s="246"/>
+      <c r="AB23" s="246"/>
+      <c r="AC23" s="246"/>
+      <c r="AD23" s="246"/>
+      <c r="AE23" s="246"/>
+      <c r="AF23" s="246"/>
+      <c r="AG23" s="246"/>
+      <c r="AH23" s="246"/>
+      <c r="AI23" s="246"/>
+      <c r="AJ23" s="246"/>
+      <c r="AK23" s="246"/>
+      <c r="AL23" s="246"/>
     </row>
     <row r="24" spans="1:38">
       <c r="A24" s="114" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B24" s="113"/>
       <c r="C24" s="113"/>
@@ -21274,7 +21711,7 @@
     </row>
     <row r="25" spans="1:38">
       <c r="A25" s="109" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B25" s="109"/>
       <c r="C25" s="109"/>
@@ -21292,7 +21729,7 @@
       <c r="O25" s="143"/>
       <c r="P25" s="143"/>
       <c r="Q25" s="72" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="R25" s="116"/>
       <c r="S25" s="116"/>
@@ -21799,7 +22236,7 @@
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
@@ -24069,17 +24506,17 @@
     </row>
     <row r="31" spans="1:38">
       <c r="A31" s="108" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G32" s="143"/>
       <c r="H32" s="143"/>
       <c r="I32" s="109" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AJ32" s="143"/>
       <c r="AK32" s="143"/>
@@ -24087,7 +24524,7 @@
     </row>
     <row r="33" spans="1:38">
       <c r="A33" s="22" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q33" s="143"/>
       <c r="R33" s="143"/>
@@ -24103,12 +24540,12 @@
       <c r="AB33" s="143"/>
       <c r="AC33" s="143"/>
       <c r="AD33" s="110" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34" spans="1:38">
       <c r="A34" s="109" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B34" s="109"/>
       <c r="C34" s="109"/>
@@ -24129,7 +24566,7 @@
       <c r="R34" s="232"/>
       <c r="S34" s="232"/>
       <c r="T34" s="22" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="U34" s="143"/>
       <c r="V34" s="143"/>
@@ -24138,7 +24575,7 @@
       <c r="Y34" s="143"/>
       <c r="Z34" s="143"/>
       <c r="AA34" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AB34" s="111"/>
       <c r="AC34" s="111"/>
@@ -24152,48 +24589,48 @@
       <c r="AL34"/>
     </row>
     <row r="35" spans="1:38">
-      <c r="A35" s="249"/>
-      <c r="B35" s="249"/>
-      <c r="C35" s="249"/>
-      <c r="D35" s="249"/>
-      <c r="E35" s="249"/>
-      <c r="F35" s="249"/>
-      <c r="G35" s="249"/>
-      <c r="H35" s="249"/>
-      <c r="I35" s="249"/>
-      <c r="J35" s="249"/>
-      <c r="K35" s="249"/>
-      <c r="L35" s="249"/>
-      <c r="M35" s="249"/>
-      <c r="N35" s="249"/>
-      <c r="O35" s="249"/>
-      <c r="P35" s="249"/>
-      <c r="Q35" s="249"/>
-      <c r="R35" s="249"/>
-      <c r="S35" s="249"/>
-      <c r="T35" s="249"/>
-      <c r="U35" s="249"/>
-      <c r="V35" s="249"/>
-      <c r="W35" s="249"/>
-      <c r="X35" s="249"/>
-      <c r="Y35" s="249"/>
-      <c r="Z35" s="249"/>
-      <c r="AA35" s="249"/>
-      <c r="AB35" s="249"/>
-      <c r="AC35" s="249"/>
-      <c r="AD35" s="249"/>
-      <c r="AE35" s="249"/>
-      <c r="AF35" s="249"/>
-      <c r="AG35" s="249"/>
-      <c r="AH35" s="249"/>
-      <c r="AI35" s="249"/>
-      <c r="AJ35" s="249"/>
-      <c r="AK35" s="249"/>
-      <c r="AL35" s="249"/>
+      <c r="A35" s="246"/>
+      <c r="B35" s="246"/>
+      <c r="C35" s="246"/>
+      <c r="D35" s="246"/>
+      <c r="E35" s="246"/>
+      <c r="F35" s="246"/>
+      <c r="G35" s="246"/>
+      <c r="H35" s="246"/>
+      <c r="I35" s="246"/>
+      <c r="J35" s="246"/>
+      <c r="K35" s="246"/>
+      <c r="L35" s="246"/>
+      <c r="M35" s="246"/>
+      <c r="N35" s="246"/>
+      <c r="O35" s="246"/>
+      <c r="P35" s="246"/>
+      <c r="Q35" s="246"/>
+      <c r="R35" s="246"/>
+      <c r="S35" s="246"/>
+      <c r="T35" s="246"/>
+      <c r="U35" s="246"/>
+      <c r="V35" s="246"/>
+      <c r="W35" s="246"/>
+      <c r="X35" s="246"/>
+      <c r="Y35" s="246"/>
+      <c r="Z35" s="246"/>
+      <c r="AA35" s="246"/>
+      <c r="AB35" s="246"/>
+      <c r="AC35" s="246"/>
+      <c r="AD35" s="246"/>
+      <c r="AE35" s="246"/>
+      <c r="AF35" s="246"/>
+      <c r="AG35" s="246"/>
+      <c r="AH35" s="246"/>
+      <c r="AI35" s="246"/>
+      <c r="AJ35" s="246"/>
+      <c r="AK35" s="246"/>
+      <c r="AL35" s="246"/>
     </row>
     <row r="36" spans="1:38">
       <c r="A36" s="114" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B36" s="113"/>
       <c r="C36" s="113"/>
@@ -24220,7 +24657,7 @@
     </row>
     <row r="37" spans="1:38">
       <c r="A37" s="109" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B37" s="109"/>
       <c r="C37" s="109"/>
@@ -24238,7 +24675,7 @@
       <c r="O37" s="143"/>
       <c r="P37" s="143"/>
       <c r="Q37" s="72" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="R37" s="116"/>
       <c r="S37" s="116"/>
@@ -32505,7 +32942,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="67" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
@@ -32603,7 +33040,7 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
@@ -32667,7 +33104,7 @@
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -32740,7 +33177,7 @@
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1">
       <c r="A9" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B9" s="29"/>
       <c r="C9" s="29"/>
@@ -32782,7 +33219,7 @@
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1">
       <c r="A10" s="179" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -32837,35 +33274,35 @@
       <c r="H11" s="179"/>
       <c r="I11" s="179"/>
       <c r="J11" s="183" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K11" s="183"/>
       <c r="L11" s="183"/>
       <c r="M11" s="183"/>
       <c r="N11" s="183"/>
       <c r="O11" s="183" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P11" s="183"/>
       <c r="Q11" s="183"/>
       <c r="R11" s="183"/>
       <c r="S11" s="183"/>
       <c r="T11" s="183" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="U11" s="183"/>
       <c r="V11" s="183"/>
       <c r="W11" s="183"/>
       <c r="X11" s="183"/>
       <c r="Y11" s="183" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z11" s="183"/>
       <c r="AA11" s="183"/>
       <c r="AB11" s="183"/>
       <c r="AC11" s="183"/>
       <c r="AD11" s="183" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AE11" s="183"/>
       <c r="AF11" s="183"/>
@@ -32881,7 +33318,7 @@
       <c r="B12" s="144"/>
       <c r="C12" s="144"/>
       <c r="D12" s="161" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E12" s="162"/>
       <c r="F12" s="162"/>
@@ -32923,7 +33360,7 @@
       <c r="B13" s="144"/>
       <c r="C13" s="144"/>
       <c r="D13" s="161" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E13" s="162"/>
       <c r="F13" s="162"/>
@@ -32965,7 +33402,7 @@
       <c r="B14" s="144"/>
       <c r="C14" s="144"/>
       <c r="D14" s="161" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E14" s="162"/>
       <c r="F14" s="162"/>
@@ -33007,7 +33444,7 @@
       <c r="B15" s="144"/>
       <c r="C15" s="144"/>
       <c r="D15" s="161" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E15" s="162"/>
       <c r="F15" s="162"/>
@@ -33046,7 +33483,7 @@
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1">
       <c r="A16" s="219" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B16" s="219"/>
       <c r="C16" s="219"/>
@@ -33128,7 +33565,7 @@
     </row>
     <row r="18" spans="1:39" ht="15" customHeight="1">
       <c r="A18" s="89" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B18" s="92"/>
       <c r="C18" s="92"/>
@@ -33170,7 +33607,7 @@
     </row>
     <row r="19" spans="1:39" ht="15" customHeight="1">
       <c r="A19" s="89" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
@@ -33203,7 +33640,7 @@
     </row>
     <row r="20" spans="1:39" ht="15" customHeight="1">
       <c r="A20" s="94" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
@@ -33236,7 +33673,7 @@
     </row>
     <row r="21" spans="1:39" ht="15" customHeight="1">
       <c r="A21" s="94" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
@@ -33269,7 +33706,7 @@
     </row>
     <row r="22" spans="1:39" ht="15" customHeight="1">
       <c r="A22" s="94" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B22" s="95"/>
       <c r="C22" s="95"/>
@@ -33312,7 +33749,7 @@
     </row>
     <row r="23" spans="1:39" ht="15" customHeight="1">
       <c r="A23" s="94" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B23" s="95"/>
       <c r="C23" s="95"/>
@@ -34323,7 +34760,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="99" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B2" s="83"/>
       <c r="C2" s="83"/>
@@ -34407,7 +34844,7 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" s="224" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B4" s="225"/>
       <c r="C4" s="225"/>
@@ -34418,7 +34855,7 @@
       <c r="H4" s="225"/>
       <c r="I4" s="226"/>
       <c r="J4" s="227" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K4" s="228"/>
       <c r="L4" s="228"/>
@@ -34428,7 +34865,7 @@
       <c r="P4" s="228"/>
       <c r="Q4" s="47"/>
       <c r="R4" s="225" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="S4" s="225"/>
       <c r="T4" s="225"/>
@@ -34437,7 +34874,7 @@
       <c r="W4" s="225"/>
       <c r="X4" s="226"/>
       <c r="Y4" s="227" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Z4" s="228"/>
       <c r="AA4" s="228"/>
@@ -34447,7 +34884,7 @@
       <c r="AE4" s="228"/>
       <c r="AF4" s="47"/>
       <c r="AG4" s="225" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AH4" s="225"/>
       <c r="AI4" s="225"/>
@@ -34937,7 +35374,7 @@
     </row>
     <row r="17" spans="1:38">
       <c r="A17" s="99" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B17" s="83"/>
       <c r="C17" s="83"/>
@@ -35021,7 +35458,7 @@
     </row>
     <row r="19" spans="1:38">
       <c r="A19" s="224" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B19" s="225"/>
       <c r="C19" s="225"/>
@@ -35032,7 +35469,7 @@
       <c r="H19" s="225"/>
       <c r="I19" s="226"/>
       <c r="J19" s="227" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K19" s="228"/>
       <c r="L19" s="228"/>
@@ -35042,7 +35479,7 @@
       <c r="P19" s="228"/>
       <c r="Q19" s="47"/>
       <c r="R19" s="225" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="S19" s="225"/>
       <c r="T19" s="225"/>
@@ -35051,7 +35488,7 @@
       <c r="W19" s="225"/>
       <c r="X19" s="226"/>
       <c r="Y19" s="227" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Z19" s="228"/>
       <c r="AA19" s="228"/>
@@ -35061,7 +35498,7 @@
       <c r="AE19" s="228"/>
       <c r="AF19" s="47"/>
       <c r="AG19" s="225" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AH19" s="225"/>
       <c r="AI19" s="225"/>
@@ -35551,12 +35988,12 @@
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="74" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" spans="1:38">
       <c r="A34" s="96" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B34" s="97"/>
       <c r="C34" s="97"/>
@@ -35598,7 +36035,7 @@
     </row>
     <row r="35" spans="1:38">
       <c r="A35" s="98" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B35" s="97"/>
       <c r="C35" s="97"/>
@@ -35640,7 +36077,7 @@
     </row>
     <row r="36" spans="1:38">
       <c r="A36" s="96" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B36" s="97"/>
       <c r="C36" s="97"/>
@@ -35682,7 +36119,7 @@
     </row>
     <row r="37" spans="1:38">
       <c r="A37" s="98" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B37" s="97"/>
       <c r="C37" s="97"/>
